--- a/Experimenten4.xlsx
+++ b/Experimenten4.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2810a0d4408f349/Documenten/GitHub/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="11_AA522F578FF748524973C9320039661620A74D1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D49114A5-2E7B-4E74-846A-BD0B3DB59132}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="11_AA522F578FF748524973C9320039661620A74D1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B120E125-EBCF-4E0D-B3F3-24D7B0705CAF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alle experimenten" sheetId="1" r:id="rId1"/>
     <sheet name="Samenvatting" sheetId="2" r:id="rId2"/>
     <sheet name="Grafiek" sheetId="4" r:id="rId3"/>
     <sheet name="Heatmap" sheetId="3" r:id="rId4"/>
+    <sheet name="SA gemiddle" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>t_max</t>
   </si>
@@ -106,12 +129,42 @@
   <si>
     <t>cooling_it = 14000</t>
   </si>
+  <si>
+    <t>&lt;-mean</t>
+  </si>
+  <si>
+    <t>^mean</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>^std</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Experiment</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="172" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,13 +172,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -140,8 +219,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -162,7 +250,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1113,6 +1201,3154 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="nl-NL"/>
+              <a:t>Invloed</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="nl-NL" baseline="0"/>
+              <a:t> van de begintemperatuur en cooling-interval op de gemiddelde penalty na SA</a:t>
+            </a:r>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.18097951577173896"/>
+          <c:y val="7.3698376988590745E-3"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA gemiddle'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>cooling_it = 100</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$A$2:$A$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$A$3:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$B$2:$B$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$B$3:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>425.76111111111095</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>390.74999999999989</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>355.97222222222223</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>364.37222222222204</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>359.87222222222215</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>384.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-248C-4D3A-B1E8-F72BF692DF92}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA gemiddle'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>cooling_it = 700</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$A$2:$A$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$A$3:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$C$2:$C$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$C$3:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>412.57777777777773</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>388.67222222222216</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>334.37222222222215</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>384.11666666666667</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>252.81111111111105</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>315.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-248C-4D3A-B1E8-F72BF692DF92}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA gemiddle'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>cooling_it = 1000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$A$2:$A$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$A$3:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$D$2:$D$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$D$3:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>340.83333333333337</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>383.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>380.50555555555547</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>371.71111111111105</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>334.13888888888891</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>332.1722222222221</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-248C-4D3A-B1E8-F72BF692DF92}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA gemiddle'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>cooling_it = 1400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$A$2:$A$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$A$3:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$E$2:$E$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$E$3:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>367.27222222222213</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>343.95555555555552</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>341.56666666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>449.72222222222217</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>392.06666666666655</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>285.12777777777774</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-248C-4D3A-B1E8-F72BF692DF92}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA gemiddle'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>cooling_it = 7000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$A$2:$A$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$A$3:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$F$2:$F$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$F$3:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>367.6722222222221</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>374.60555555555555</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>366.1444444444445</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>299.24444444444447</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>333.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>358.63333333333327</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-248C-4D3A-B1E8-F72BF692DF92}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA gemiddle'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>cooling_it = 14000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$A$2:$A$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$A$3:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'SA gemiddle'!$G$2:$G$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'SA gemiddle'!$G$3:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>340.91111111111115</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>314.52222222222213</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>310.35000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>353.84444444444443</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>350.01666666666671</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>433.67777777777781</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-248C-4D3A-B1E8-F72BF692DF92}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="105630399"/>
+        <c:axId val="105629439"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="105630399"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Begintemperatuur (temp)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="105629439"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="105629439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Gemiddelde totale penalty na SA</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="105630399"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="nl-NL"/>
+              <a:t>Gemiddelde</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="nl-NL" baseline="0"/>
+              <a:t> totale penalty per temperatuur </a:t>
+            </a:r>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{3E0E6033-A0FD-49EC-AC80-D988000F97A6}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-EE49-43D7-BE6E-B83F6DC7446D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{360AE5AB-B86B-4A54-BC1F-B542F45BB3D0}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-EE49-43D7-BE6E-B83F6DC7446D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{34660299-A55B-4096-B652-C64AD22F656D}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-EE49-43D7-BE6E-B83F6DC7446D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{6DB89E89-A74F-42B4-81C2-1942993A59FD}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-EE49-43D7-BE6E-B83F6DC7446D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{88DA0426-56C0-418C-992F-EF1A1510D282}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-EE49-43D7-BE6E-B83F6DC7446D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{1BA6F217-5EEE-4C1B-85A7-B96E89B8CD2E}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-EE49-43D7-BE6E-B83F6DC7446D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'SA gemiddle'!$A$3:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SA gemiddle'!$I$3:$I$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>365.8533333333333</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>361.03111111111104</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>355.64722222222224</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>376.19861111111112</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>328.07916666666659</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>322.85833333333329</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'SA gemiddle'!$J$3:$J$8</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="6"/>
+                  <c:pt idx="0">
+                    <c:v>101,3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>116,7</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>73,8</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>101,0</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>106,7</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>105,5</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EE49-43D7-BE6E-B83F6DC7446D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1537301903"/>
+        <c:axId val="1537302383"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1537301903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Temperatuur</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1537302383"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1537302383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Gemidddlede</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="nl-NL" baseline="0"/>
+                  <a:t> t</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>otale</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="nl-NL" baseline="0"/>
+                  <a:t> penalty</a:t>
+                </a:r>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1537301903"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="nl-NL"/>
+              <a:t>Gemiddelde totale penalty per cooling</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="nl-NL" baseline="0"/>
+              <a:t> iteraties</a:t>
+            </a:r>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C1B3A0DC-BEFE-4012-A010-167B628ACE00}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-FEF3-4871-AFD9-4018A3B16FFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{B6B3DC73-A616-41D8-816F-2413E5E8ECB7}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-FEF3-4871-AFD9-4018A3B16FFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{25E7426F-68D7-48A3-9758-B899E3E1523E}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-FEF3-4871-AFD9-4018A3B16FFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{AA0C8A97-DDAB-4919-8F6C-F8C5BD6C31BF}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-FEF3-4871-AFD9-4018A3B16FFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F9513D3B-BCE1-43FD-9A56-477A7A0004B1}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-FEF3-4871-AFD9-4018A3B16FFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{1D3C9147-2673-417D-A0E7-F0D13BAF1979}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-FEF3-4871-AFD9-4018A3B16FFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'SA gemiddle'!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>cooling_it = 100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>cooling_it = 700</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>cooling_it = 1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>cooling_it = 1400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cooling_it = 7000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>cooling_it = 14000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SA gemiddle'!$B$11:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>366.22916666666657</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>321.69999999999993</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>354.63194444444434</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>367.12083333333328</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>339.33055555555552</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>361.97222222222229</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'SA gemiddle'!$B$12:$G$12</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="6"/>
+                  <c:pt idx="0">
+                    <c:v>79,4</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>110,3</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>51,6</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>122,0</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>70,7</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>128,1</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FEF3-4871-AFD9-4018A3B16FFC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1107552911"/>
+        <c:axId val="1107556751"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1107552911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Cooling iteraties</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1107556751"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1107556751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Gemiddelde totale penalty</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1107552911"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="nl-NL"/>
+              <a:t>Gemiddelde</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="nl-NL" baseline="0"/>
+              <a:t> totale penalty per temperatuur </a:t>
+            </a:r>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F034B9C6-57A6-4724-9268-C025B9CDECA6}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-5395-45D0-8F40-A094916972B7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{AAFDCA52-015B-42C2-BF4B-8132C0F67D74}" type="CELLRANGE">
+                      <a:rPr lang="nl-NL"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-5395-45D0-8F40-A094916972B7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C5C45CF1-A84F-408F-B10A-F69D67EC5214}" type="CELLRANGE">
+                      <a:rPr lang="nl-NL"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-5395-45D0-8F40-A094916972B7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{BF9B62AD-956B-4C17-866E-978DD15A7EF1}" type="CELLRANGE">
+                      <a:rPr lang="nl-NL"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-5395-45D0-8F40-A094916972B7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{778779C7-E389-4837-A4AC-353503F054E5}" type="CELLRANGE">
+                      <a:rPr lang="nl-NL"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-5395-45D0-8F40-A094916972B7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'SA gemiddle'!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>750</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SA gemiddle'!$I$5:$I$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>355.64722222222224</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>376.19861111111112</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>328.07916666666659</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>322.85833333333329</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>365.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'SA gemiddle'!$J$5:$J$9</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="5"/>
+                  <c:pt idx="0">
+                    <c:v>73,8</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>101,0</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>106,7</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>105,5</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>103,2</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-5395-45D0-8F40-A094916972B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1537301903"/>
+        <c:axId val="1537302383"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1537301903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Temperatuur</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1537302383"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1537302383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Gemidddlede</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="nl-NL" baseline="0"/>
+                  <a:t> t</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>otale</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="nl-NL" baseline="0"/>
+                  <a:t> penalty</a:t>
+                </a:r>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1537301903"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1150,6 +4386,95 @@
     <a:lumMod val="50000"/>
     <a:lumOff val="50000"/>
   </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
 </cs:colorStyle>
 </file>
 
@@ -1656,20 +4981,2032 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>504824</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>85726</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>263524</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>200024</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>155574</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1689,6 +7026,157 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3174</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3280AAC-221E-1021-8EE8-DA04FE21EBC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CA2AC8F-2BCE-9569-2142-5F8611FAC181}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>606424</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>317499</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE16DA55-E013-8787-0455-AC7579633B6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0845DD4-E800-40F5-AECF-99231CDA4AB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1983,22 +7471,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K211"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.36328125" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2033,7 +7521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>70000</v>
       </c>
@@ -2068,7 +7556,7 @@
         <v>5.4862403999868548</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>70000</v>
       </c>
@@ -2103,7 +7591,7 @@
         <v>5.2879847000149311</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>70000</v>
       </c>
@@ -2138,7 +7626,7 @@
         <v>5.3286113000067417</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>70000</v>
       </c>
@@ -2173,7 +7661,7 @@
         <v>5.4278759000007986</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>70000</v>
       </c>
@@ -2208,7 +7696,7 @@
         <v>5.3958127999940189</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>70000</v>
       </c>
@@ -2243,7 +7731,7 @@
         <v>5.4214574999932674</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>70000</v>
       </c>
@@ -2278,7 +7766,7 @@
         <v>5.5024398000095971</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>70000</v>
       </c>
@@ -2313,7 +7801,7 @@
         <v>5.4252568999945652</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>70000</v>
       </c>
@@ -2348,7 +7836,7 @@
         <v>5.4009593999944627</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>70000</v>
       </c>
@@ -2383,7 +7871,7 @@
         <v>5.352932800000417</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>70000</v>
       </c>
@@ -2418,7 +7906,7 @@
         <v>5.4586825000005774</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>70000</v>
       </c>
@@ -2453,7 +7941,7 @@
         <v>5.3676586999936262</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>70000</v>
       </c>
@@ -2488,7 +7976,7 @@
         <v>5.4901777999912156</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>70000</v>
       </c>
@@ -2523,7 +8011,7 @@
         <v>5.4918017000018153</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>70000</v>
       </c>
@@ -2558,7 +8046,7 @@
         <v>5.4781649000069592</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>70000</v>
       </c>
@@ -2593,7 +8081,7 @@
         <v>5.4684198000177284</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>70000</v>
       </c>
@@ -2628,7 +8116,7 @@
         <v>5.3366022999980487</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>70000</v>
       </c>
@@ -2663,7 +8151,7 @@
         <v>5.4007717999920706</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>70000</v>
       </c>
@@ -2698,7 +8186,7 @@
         <v>5.6570938000077149</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>70000</v>
       </c>
@@ -2733,7 +8221,7 @@
         <v>5.4854627999884542</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>70000</v>
       </c>
@@ -2768,7 +8256,7 @@
         <v>5.5464021999941906</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>70000</v>
       </c>
@@ -2803,7 +8291,7 @@
         <v>5.3863133000122616</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>70000</v>
       </c>
@@ -2838,7 +8326,7 @@
         <v>5.4932814999920083</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>70000</v>
       </c>
@@ -2873,7 +8361,7 @@
         <v>5.4605587999976706</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>70000</v>
       </c>
@@ -2908,7 +8396,7 @@
         <v>5.6403131999977631</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>70000</v>
       </c>
@@ -2943,7 +8431,7 @@
         <v>5.3710718999936944</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>70000</v>
       </c>
@@ -2978,7 +8466,7 @@
         <v>5.8363017999945441</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>70000</v>
       </c>
@@ -3013,7 +8501,7 @@
         <v>5.993630499986466</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>70000</v>
       </c>
@@ -3048,7 +8536,7 @@
         <v>5.4403558000049088</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>70000</v>
       </c>
@@ -3083,7 +8571,7 @@
         <v>5.4401070000021718</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>70000</v>
       </c>
@@ -3118,7 +8606,7 @@
         <v>5.2861697000043932</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>70000</v>
       </c>
@@ -3153,7 +8641,7 @@
         <v>5.4719046999962302</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>70000</v>
       </c>
@@ -3188,7 +8676,7 @@
         <v>5.4979333000082988</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>70000</v>
       </c>
@@ -3223,7 +8711,7 @@
         <v>5.454824299988104</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>70000</v>
       </c>
@@ -3258,7 +8746,7 @@
         <v>5.6091917999874568</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>70000</v>
       </c>
@@ -3293,7 +8781,7 @@
         <v>5.4541254000214394</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>70000</v>
       </c>
@@ -3328,7 +8816,7 @@
         <v>5.4252436999959173</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>70000</v>
       </c>
@@ -3363,7 +8851,7 @@
         <v>5.4914328000013484</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>70000</v>
       </c>
@@ -3398,7 +8886,7 @@
         <v>5.4799296999844964</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>70000</v>
       </c>
@@ -3433,7 +8921,7 @@
         <v>5.4780500999913784</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>70000</v>
       </c>
@@ -3468,7 +8956,7 @@
         <v>5.5036676000017906</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>70000</v>
       </c>
@@ -3503,7 +8991,7 @@
         <v>5.4968678000004729</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>70000</v>
       </c>
@@ -3538,7 +9026,7 @@
         <v>5.5327691999991657</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>70000</v>
       </c>
@@ -3573,7 +9061,7 @@
         <v>5.6293098999885842</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>70000</v>
       </c>
@@ -3608,7 +9096,7 @@
         <v>5.4928616999968654</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>70000</v>
       </c>
@@ -3643,7 +9131,7 @@
         <v>5.3971242000116044</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>70000</v>
       </c>
@@ -3678,7 +9166,7 @@
         <v>5.5474619000015082</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>70000</v>
       </c>
@@ -3713,7 +9201,7 @@
         <v>5.6888022999919494</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>70000</v>
       </c>
@@ -3748,7 +9236,7 @@
         <v>5.4545953999913763</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>70000</v>
       </c>
@@ -3783,7 +9271,7 @@
         <v>5.5183144000038737</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>70000</v>
       </c>
@@ -3818,7 +9306,7 @@
         <v>5.4005103999952553</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>70000</v>
       </c>
@@ -3853,7 +9341,7 @@
         <v>5.441641699988395</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>70000</v>
       </c>
@@ -3888,7 +9376,7 @@
         <v>5.5560860999976276</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>70000</v>
       </c>
@@ -3923,7 +9411,7 @@
         <v>5.458142500006943</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>70000</v>
       </c>
@@ -3958,7 +9446,7 @@
         <v>5.4442836000089301</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>70000</v>
       </c>
@@ -3993,7 +9481,7 @@
         <v>5.4848492999881273</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>70000</v>
       </c>
@@ -4028,7 +9516,7 @@
         <v>5.4112370999937411</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>70000</v>
       </c>
@@ -4063,7 +9551,7 @@
         <v>5.5142770999955246</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>70000</v>
       </c>
@@ -4098,7 +9586,7 @@
         <v>5.5159693000023253</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>70000</v>
       </c>
@@ -4133,7 +9621,7 @@
         <v>5.4517025999957696</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>70000</v>
       </c>
@@ -4168,7 +9656,7 @@
         <v>5.383823800002574</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>70000</v>
       </c>
@@ -4203,7 +9691,7 @@
         <v>5.5494637999945553</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>70000</v>
       </c>
@@ -4238,7 +9726,7 @@
         <v>5.2907038999983342</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>70000</v>
       </c>
@@ -4273,7 +9761,7 @@
         <v>5.3541529000067376</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>70000</v>
       </c>
@@ -4308,7 +9796,7 @@
         <v>5.2348554999916814</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>70000</v>
       </c>
@@ -4343,7 +9831,7 @@
         <v>5.5762047999887727</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>70000</v>
       </c>
@@ -4378,7 +9866,7 @@
         <v>5.4850226000125986</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>70000</v>
       </c>
@@ -4413,7 +9901,7 @@
         <v>5.5608098000084283</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>70000</v>
       </c>
@@ -4448,7 +9936,7 @@
         <v>5.4910147000045981</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70000</v>
       </c>
@@ -4483,7 +9971,7 @@
         <v>5.4554984999995213</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70000</v>
       </c>
@@ -4518,7 +10006,7 @@
         <v>5.4882175000093412</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>70000</v>
       </c>
@@ -4553,7 +10041,7 @@
         <v>5.4942360000131876</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>70000</v>
       </c>
@@ -4588,7 +10076,7 @@
         <v>5.6580567999917548</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>70000</v>
       </c>
@@ -4623,7 +10111,7 @@
         <v>5.4267287999973632</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>70000</v>
       </c>
@@ -4658,7 +10146,7 @@
         <v>5.4175782000093022</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>70000</v>
       </c>
@@ -4693,7 +10181,7 @@
         <v>5.5764956999919377</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>70000</v>
       </c>
@@ -4728,7 +10216,7 @@
         <v>5.5175904999923659</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>70000</v>
       </c>
@@ -4763,7 +10251,7 @@
         <v>5.5198772999865469</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>70000</v>
       </c>
@@ -4798,7 +10286,7 @@
         <v>5.5172108999977354</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>70000</v>
       </c>
@@ -4833,7 +10321,7 @@
         <v>5.3989683999971021</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>70000</v>
       </c>
@@ -4868,7 +10356,7 @@
         <v>5.5347767999919597</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>70000</v>
       </c>
@@ -4903,7 +10391,7 @@
         <v>5.6479407000151696</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>70000</v>
       </c>
@@ -4938,7 +10426,7 @@
         <v>5.4130385000025854</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>70000</v>
       </c>
@@ -4973,7 +10461,7 @@
         <v>5.4161419000156457</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>70000</v>
       </c>
@@ -5008,7 +10496,7 @@
         <v>5.4464356000098633</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>70000</v>
       </c>
@@ -5043,7 +10531,7 @@
         <v>5.6166250000096616</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>70000</v>
       </c>
@@ -5078,7 +10566,7 @@
         <v>5.5304822000034619</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>70000</v>
       </c>
@@ -5113,7 +10601,7 @@
         <v>5.5718799000023864</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>70000</v>
       </c>
@@ -5148,7 +10636,7 @@
         <v>5.5633484999852953</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>70000</v>
       </c>
@@ -5183,7 +10671,7 @@
         <v>5.5850031000009039</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>70000</v>
       </c>
@@ -5218,7 +10706,7 @@
         <v>5.5347347000060836</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>70000</v>
       </c>
@@ -5253,7 +10741,7 @@
         <v>5.3718701000034343</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>70000</v>
       </c>
@@ -5288,7 +10776,7 @@
         <v>5.503811599992332</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>70000</v>
       </c>
@@ -5323,7 +10811,7 @@
         <v>5.4048397000005934</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>70000</v>
       </c>
@@ -5358,7 +10846,7 @@
         <v>5.3995544999925187</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>70000</v>
       </c>
@@ -5393,7 +10881,7 @@
         <v>5.5285912999970606</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>70000</v>
       </c>
@@ -5428,7 +10916,7 @@
         <v>5.4736036000103923</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>70000</v>
       </c>
@@ -5463,7 +10951,7 @@
         <v>5.5013610000023618</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>70000</v>
       </c>
@@ -5498,7 +10986,7 @@
         <v>5.4882464999973308</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>70000</v>
       </c>
@@ -5533,7 +11021,7 @@
         <v>5.5281380000087674</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>70000</v>
       </c>
@@ -5568,7 +11056,7 @@
         <v>5.4136193999875104</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>70000</v>
       </c>
@@ -5603,7 +11091,7 @@
         <v>5.617174500002875</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>70000</v>
       </c>
@@ -5638,7 +11126,7 @@
         <v>5.5348951000196394</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>70000</v>
       </c>
@@ -5673,7 +11161,7 @@
         <v>5.5336121999862371</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>70000</v>
       </c>
@@ -5708,7 +11196,7 @@
         <v>5.5184537000022829</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>70000</v>
       </c>
@@ -5743,7 +11231,7 @@
         <v>5.7365925000049174</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>70000</v>
       </c>
@@ -5778,7 +11266,7 @@
         <v>5.4973973999876762</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>70000</v>
       </c>
@@ -5813,7 +11301,7 @@
         <v>5.4988298999960534</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>70000</v>
       </c>
@@ -5848,7 +11336,7 @@
         <v>5.5905288999929326</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>70000</v>
       </c>
@@ -5883,7 +11371,7 @@
         <v>5.4938764999969862</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>70000</v>
       </c>
@@ -5918,7 +11406,7 @@
         <v>5.3953062999935364</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>70000</v>
       </c>
@@ -5953,7 +11441,7 @@
         <v>5.6602434999949756</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>70000</v>
       </c>
@@ -5988,7 +11476,7 @@
         <v>5.6454630000080206</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>70000</v>
       </c>
@@ -6023,7 +11511,7 @@
         <v>5.5846527999965474</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>70000</v>
       </c>
@@ -6058,7 +11546,7 @@
         <v>5.5755204999877606</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>70000</v>
       </c>
@@ -6093,7 +11581,7 @@
         <v>5.6009620999975596</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>70000</v>
       </c>
@@ -6128,7 +11616,7 @@
         <v>5.6116392999974778</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>70000</v>
       </c>
@@ -6163,7 +11651,7 @@
         <v>5.5959707000001799</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>70000</v>
       </c>
@@ -6198,7 +11686,7 @@
         <v>5.6165087999979733</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>70000</v>
       </c>
@@ -6233,7 +11721,7 @@
         <v>5.6554116999905091</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>70000</v>
       </c>
@@ -6268,7 +11756,7 @@
         <v>5.4286443000019062</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>70000</v>
       </c>
@@ -6303,7 +11791,7 @@
         <v>5.4205696999997599</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>70000</v>
       </c>
@@ -6338,7 +11826,7 @@
         <v>5.3985808999859728</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>70000</v>
       </c>
@@ -6373,7 +11861,7 @@
         <v>5.3885965999943437</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>70000</v>
       </c>
@@ -6408,7 +11896,7 @@
         <v>5.5135240000090562</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>70000</v>
       </c>
@@ -6443,7 +11931,7 @@
         <v>5.6957664000074146</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>70000</v>
       </c>
@@ -6478,7 +11966,7 @@
         <v>5.6080256000132067</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>70000</v>
       </c>
@@ -6513,7 +12001,7 @@
         <v>5.7904736999917077</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>70000</v>
       </c>
@@ -6548,7 +12036,7 @@
         <v>5.4898987999913524</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>70000</v>
       </c>
@@ -6583,7 +12071,7 @@
         <v>5.5945358000026317</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>70000</v>
       </c>
@@ -6618,7 +12106,7 @@
         <v>5.5469640000083018</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>70000</v>
       </c>
@@ -6653,7 +12141,7 @@
         <v>5.4908743999985754</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>70000</v>
       </c>
@@ -6688,7 +12176,7 @@
         <v>5.5923691999923903</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>70000</v>
       </c>
@@ -6723,7 +12211,7 @@
         <v>5.632353900000453</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>70000</v>
       </c>
@@ -6758,7 +12246,7 @@
         <v>5.3709352999867406</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>70000</v>
       </c>
@@ -6793,7 +12281,7 @@
         <v>5.6315172999893548</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>70000</v>
       </c>
@@ -6828,7 +12316,7 @@
         <v>5.5436397000012221</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>70000</v>
       </c>
@@ -6863,7 +12351,7 @@
         <v>5.6179967000061879</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>70000</v>
       </c>
@@ -6898,7 +12386,7 @@
         <v>5.5271779999893624</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>70000</v>
       </c>
@@ -6933,7 +12421,7 @@
         <v>5.4870652999961749</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>70000</v>
       </c>
@@ -6968,7 +12456,7 @@
         <v>5.6252593999961391</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>70000</v>
       </c>
@@ -7003,7 +12491,7 @@
         <v>5.609474400000181</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>70000</v>
       </c>
@@ -7038,7 +12526,7 @@
         <v>5.5344228999892948</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>70000</v>
       </c>
@@ -7073,7 +12561,7 @@
         <v>5.66388820001157</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>70000</v>
       </c>
@@ -7108,7 +12596,7 @@
         <v>5.6976474000111921</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>70000</v>
       </c>
@@ -7143,7 +12631,7 @@
         <v>5.483169099999941</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>70000</v>
       </c>
@@ -7178,7 +12666,7 @@
         <v>5.6228725999972076</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>70000</v>
       </c>
@@ -7213,7 +12701,7 @@
         <v>5.5762456999946153</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>70000</v>
       </c>
@@ -7248,7 +12736,7 @@
         <v>5.6415805999859003</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>70000</v>
       </c>
@@ -7283,7 +12771,7 @@
         <v>5.4804294000059599</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>70000</v>
       </c>
@@ -7318,7 +12806,7 @@
         <v>5.3574181000003591</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>70000</v>
       </c>
@@ -7353,7 +12841,7 @@
         <v>5.3712397999915993</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>70000</v>
       </c>
@@ -7388,7 +12876,7 @@
         <v>5.4004716000054032</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>70000</v>
       </c>
@@ -7423,7 +12911,7 @@
         <v>5.3194586999888998</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>70000</v>
       </c>
@@ -7458,7 +12946,7 @@
         <v>5.6496053999871947</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>70000</v>
       </c>
@@ -7493,7 +12981,7 @@
         <v>5.5344863999926019</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>70000</v>
       </c>
@@ -7528,7 +13016,7 @@
         <v>5.5536712000030093</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>70000</v>
       </c>
@@ -7563,7 +13051,7 @@
         <v>5.5071129000134533</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>70000</v>
       </c>
@@ -7598,7 +13086,7 @@
         <v>5.5292266000033123</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>70000</v>
       </c>
@@ -7633,7 +13121,7 @@
         <v>5.4909938999917358</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>70000</v>
       </c>
@@ -7668,7 +13156,7 @@
         <v>5.5465432000055443</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>70000</v>
       </c>
@@ -7703,7 +13191,7 @@
         <v>5.4590059999900404</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>70000</v>
       </c>
@@ -7738,7 +13226,7 @@
         <v>5.4736427000170806</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>70000</v>
       </c>
@@ -7773,7 +13261,7 @@
         <v>5.9256452000117861</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>70000</v>
       </c>
@@ -7808,7 +13296,7 @@
         <v>8.7022127999953227</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>70000</v>
       </c>
@@ -7843,7 +13331,7 @@
         <v>7.5487007000047024</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>70000</v>
       </c>
@@ -7878,7 +13366,7 @@
         <v>5.7690268000005744</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>70000</v>
       </c>
@@ -7913,7 +13401,7 @@
         <v>5.1563337999978103</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>70000</v>
       </c>
@@ -7948,7 +13436,7 @@
         <v>5.1824070000002393</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>70000</v>
       </c>
@@ -7983,7 +13471,7 @@
         <v>6.3845861000008881</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>70000</v>
       </c>
@@ -8018,7 +13506,7 @@
         <v>5.1972315000020899</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>70000</v>
       </c>
@@ -8053,7 +13541,7 @@
         <v>4.7006769999861717</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>70000</v>
       </c>
@@ -8088,7 +13576,7 @@
         <v>4.5645587999897543</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>70000</v>
       </c>
@@ -8123,7 +13611,7 @@
         <v>4.5141120000043884</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>70000</v>
       </c>
@@ -8158,7 +13646,7 @@
         <v>4.864603400012129</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>70000</v>
       </c>
@@ -8193,7 +13681,7 @@
         <v>4.4946021000068868</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>70000</v>
       </c>
@@ -8228,7 +13716,7 @@
         <v>4.5765301000210457</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>70000</v>
       </c>
@@ -8263,7 +13751,7 @@
         <v>4.6624580000061542</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>70000</v>
       </c>
@@ -8298,7 +13786,7 @@
         <v>4.5590339000045788</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>70000</v>
       </c>
@@ -8333,7 +13821,7 @@
         <v>5.2118497000046773</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>70000</v>
       </c>
@@ -8368,7 +13856,7 @@
         <v>4.8484873000124944</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>70000</v>
       </c>
@@ -8403,7 +13891,7 @@
         <v>4.5169654000201263</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>70000</v>
       </c>
@@ -8438,7 +13926,7 @@
         <v>4.6380415999883553</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>70000</v>
       </c>
@@ -8473,7 +13961,7 @@
         <v>4.6955578999913996</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>70000</v>
       </c>
@@ -8508,7 +13996,7 @@
         <v>4.5501588999904934</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>70000</v>
       </c>
@@ -8543,7 +14031,7 @@
         <v>4.5285080999892671</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>70000</v>
       </c>
@@ -8578,7 +14066,7 @@
         <v>4.5849701999977697</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>70000</v>
       </c>
@@ -8613,7 +14101,7 @@
         <v>4.7370612999948207</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>70000</v>
       </c>
@@ -8648,7 +14136,7 @@
         <v>4.6931349999940721</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>70000</v>
       </c>
@@ -8683,7 +14171,7 @@
         <v>4.5657396000169683</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>70000</v>
       </c>
@@ -8718,7 +14206,7 @@
         <v>4.6579338999872562</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>70000</v>
       </c>
@@ -8753,7 +14241,7 @@
         <v>4.8646519999892917</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>70000</v>
       </c>
@@ -8788,7 +14276,7 @@
         <v>5.261319099998218</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>70000</v>
       </c>
@@ -8823,7 +14311,7 @@
         <v>5.0402452999987872</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>70000</v>
       </c>
@@ -8858,7 +14346,7 @@
         <v>5.3113833999959752</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>70000</v>
       </c>
@@ -8893,7 +14381,7 @@
         <v>4.628458999999566</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>70000</v>
       </c>
@@ -8928,7 +14416,7 @@
         <v>4.6917124000028707</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>70000</v>
       </c>
@@ -8963,7 +14451,7 @@
         <v>4.6777011999947717</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>70000</v>
       </c>
@@ -8998,7 +14486,7 @@
         <v>4.6111103000148432</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>70000</v>
       </c>
@@ -9033,7 +14521,7 @@
         <v>4.7697809999954188</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>70000</v>
       </c>
@@ -9068,7 +14556,7 @@
         <v>4.8671342999878107</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>70000</v>
       </c>
@@ -9103,7 +14591,7 @@
         <v>5.1215529999899454</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>70000</v>
       </c>
@@ -9138,7 +14626,7 @@
         <v>4.5786801999929594</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>70000</v>
       </c>
@@ -9173,7 +14661,7 @@
         <v>4.4873394000169364</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>70000</v>
       </c>
@@ -9208,7 +14696,7 @@
         <v>4.3980791999929352</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>70000</v>
       </c>
@@ -9243,7 +14731,7 @@
         <v>4.4200246999971569</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>70000</v>
       </c>
@@ -9278,7 +14766,7 @@
         <v>4.4822079000005033</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>70000</v>
       </c>
@@ -9313,7 +14801,7 @@
         <v>4.4898767999984557</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>70000</v>
       </c>
@@ -9348,7 +14836,7 @@
         <v>4.4411232999991634</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>70000</v>
       </c>
@@ -9391,18 +14879,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -9425,7 +14913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>50</v>
       </c>
@@ -9448,7 +14936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>50</v>
       </c>
@@ -9471,7 +14959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>50</v>
       </c>
@@ -9494,7 +14982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>50</v>
       </c>
@@ -9517,7 +15005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>50</v>
       </c>
@@ -9540,7 +15028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>50</v>
       </c>
@@ -9563,7 +15051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>80</v>
       </c>
@@ -9586,7 +15074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>80</v>
       </c>
@@ -9609,7 +15097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>80</v>
       </c>
@@ -9632,7 +15120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>80</v>
       </c>
@@ -9655,7 +15143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>80</v>
       </c>
@@ -9678,7 +15166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>80</v>
       </c>
@@ -9701,7 +15189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>100</v>
       </c>
@@ -9724,7 +15212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>100</v>
       </c>
@@ -9747,7 +15235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>100</v>
       </c>
@@ -9770,7 +15258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>100</v>
       </c>
@@ -9793,7 +15281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>100</v>
       </c>
@@ -9816,7 +15304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>100</v>
       </c>
@@ -9839,7 +15327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>120</v>
       </c>
@@ -9862,7 +15350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>120</v>
       </c>
@@ -9885,7 +15373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>120</v>
       </c>
@@ -9908,7 +15396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>120</v>
       </c>
@@ -9931,7 +15419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>120</v>
       </c>
@@ -9954,7 +15442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>120</v>
       </c>
@@ -9977,7 +15465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>150</v>
       </c>
@@ -10000,7 +15488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>150</v>
       </c>
@@ -10023,7 +15511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>150</v>
       </c>
@@ -10046,7 +15534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>150</v>
       </c>
@@ -10069,7 +15557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>150</v>
       </c>
@@ -10092,7 +15580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>150</v>
       </c>
@@ -10115,7 +15603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>200</v>
       </c>
@@ -10138,7 +15626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>200</v>
       </c>
@@ -10161,7 +15649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>200</v>
       </c>
@@ -10184,7 +15672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>200</v>
       </c>
@@ -10207,7 +15695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>200</v>
       </c>
@@ -10230,7 +15718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>200</v>
       </c>
@@ -10253,7 +15741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>500</v>
       </c>
@@ -10276,7 +15764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>500</v>
       </c>
@@ -10299,7 +15787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>500</v>
       </c>
@@ -10322,7 +15810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>500</v>
       </c>
@@ -10345,7 +15833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>500</v>
       </c>
@@ -10368,7 +15856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>500</v>
       </c>
@@ -10398,15 +15886,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E265F2D-4BDB-4332-91AD-88FABCDE77F4}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -10429,7 +15917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>50</v>
       </c>
@@ -10457,8 +15945,12 @@
         <f>SUMIFS(Samenvatting!$C$2:$C$43,Samenvatting!$A$2:$A$43,$A2,Samenvatting!$B$2:$B$43,VALUE(SUBSTITUTE(G$1,"cooling_it = ","")))</f>
         <v>361.72222222222217</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <f>AVERAGE(B2:G2)</f>
+        <v>525.25370370370365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>80</v>
       </c>
@@ -10486,8 +15978,12 @@
         <f>SUMIFS(Samenvatting!$C$2:$C$43,Samenvatting!$A$2:$A$43,$A3,Samenvatting!$B$2:$B$43,VALUE(SUBSTITUTE(G$1,"cooling_it = ","")))</f>
         <v>340.91111111111121</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <f t="shared" ref="I3:I8" si="0">AVERAGE(B3:G3)</f>
+        <v>370.11018518518512</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>100</v>
       </c>
@@ -10515,8 +16011,12 @@
         <f>SUMIFS(Samenvatting!$C$2:$C$43,Samenvatting!$A$2:$A$43,$A4,Samenvatting!$B$2:$B$43,VALUE(SUBSTITUTE(G$1,"cooling_it = ","")))</f>
         <v>313.8555555555555</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>364.9175925925926</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>120</v>
       </c>
@@ -10544,8 +16044,12 @@
         <f>SUMIFS(Samenvatting!$C$2:$C$43,Samenvatting!$A$2:$A$43,$A5,Samenvatting!$B$2:$B$43,VALUE(SUBSTITUTE(G$1,"cooling_it = ","")))</f>
         <v>305.91666666666669</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>337.22222222222223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>150</v>
       </c>
@@ -10573,8 +16077,12 @@
         <f>SUMIFS(Samenvatting!$C$2:$C$43,Samenvatting!$A$2:$A$43,$A6,Samenvatting!$B$2:$B$43,VALUE(SUBSTITUTE(G$1,"cooling_it = ","")))</f>
         <v>353.51111111111112</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>363.35092592592588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>200</v>
       </c>
@@ -10602,8 +16110,12 @@
         <f>SUMIFS(Samenvatting!$C$2:$C$43,Samenvatting!$A$2:$A$43,$A7,Samenvatting!$B$2:$B$43,VALUE(SUBSTITUTE(G$1,"cooling_it = ","")))</f>
         <v>350.01666666666671</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>330.38425925925918</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>500</v>
       </c>
@@ -10630,6 +16142,36 @@
       <c r="G8">
         <f>SUMIFS(Samenvatting!$C$2:$C$43,Samenvatting!$A$2:$A$43,$A8,Samenvatting!$B$2:$B$43,VALUE(SUBSTITUTE(G$1,"cooling_it = ","")))</f>
         <v>430.31111111111107</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>347.58518518518514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B10">
+        <f>AVERAGE(B2:B8)</f>
+        <v>388.05238095238076</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ref="C10:G10" si="1">AVERAGE(C2:C8)</f>
+        <v>382.21825396825392</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>395.95476190476177</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>370.95793650793649</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>373.77380952380958</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>350.89206349206353</v>
       </c>
     </row>
   </sheetData>
@@ -10641,9 +16183,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -10666,7 +16208,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>50</v>
       </c>
@@ -10689,7 +16231,7 @@
         <v>361.72222222222217</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>80</v>
       </c>
@@ -10712,7 +16254,7 @@
         <v>340.91111111111121</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>100</v>
       </c>
@@ -10735,7 +16277,7 @@
         <v>313.8555555555555</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>120</v>
       </c>
@@ -10758,7 +16300,7 @@
         <v>305.91666666666669</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>150</v>
       </c>
@@ -10781,7 +16323,7 @@
         <v>353.51111111111112</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>200</v>
       </c>
@@ -10804,7 +16346,7 @@
         <v>350.01666666666671</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>500</v>
       </c>
@@ -10830,4 +16372,415 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD075B78-C560-45B4-82DD-6832EAF8A444}">
+  <dimension ref="A1:N50"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>50</v>
+      </c>
+      <c r="B2" s="1">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A2,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
+        <v>490.90555555555528</v>
+      </c>
+      <c r="C2" s="1">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A2,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
+        <v>631.79444444444425</v>
+      </c>
+      <c r="D2" s="1">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A2,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
+        <v>636.75555555555525</v>
+      </c>
+      <c r="E2" s="1">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A2,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
+        <v>479.70555555555546</v>
+      </c>
+      <c r="F2" s="1">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A2,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
+        <v>568.11111111111109</v>
+      </c>
+      <c r="G2" s="1">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A2,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
+        <v>362.92222222222222</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="N2" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>80</v>
+      </c>
+      <c r="B3" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A3,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
+        <v>425.76111111111095</v>
+      </c>
+      <c r="C3" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A3,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
+        <v>412.57777777777773</v>
+      </c>
+      <c r="D3" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A3,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
+        <v>340.83333333333337</v>
+      </c>
+      <c r="E3" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A3,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
+        <v>367.27222222222213</v>
+      </c>
+      <c r="F3" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A3,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
+        <v>367.6722222222221</v>
+      </c>
+      <c r="G3" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A3,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
+        <v>340.91111111111115</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2">
+        <f>AVERAGE(C3:G3)</f>
+        <v>365.8533333333333</v>
+      </c>
+      <c r="J3" s="5" cm="1">
+        <f t="array" ref="J3">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A3))</f>
+        <v>101.25638696181393</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>100</v>
+      </c>
+      <c r="B4" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A4,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
+        <v>390.74999999999989</v>
+      </c>
+      <c r="C4" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A4,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
+        <v>388.67222222222216</v>
+      </c>
+      <c r="D4" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A4,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
+        <v>383.4</v>
+      </c>
+      <c r="E4" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A4,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
+        <v>343.95555555555552</v>
+      </c>
+      <c r="F4" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A4,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
+        <v>374.60555555555555</v>
+      </c>
+      <c r="G4" s="2">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A4,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
+        <v>314.52222222222213</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2">
+        <f t="shared" ref="I4" si="0">AVERAGE(C4:G4)</f>
+        <v>361.03111111111104</v>
+      </c>
+      <c r="J4" s="5" cm="1">
+        <f t="array" ref="J4">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A4))</f>
+        <v>116.72029457180238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>120</v>
+      </c>
+      <c r="B5" s="6">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
+        <v>355.97222222222223</v>
+      </c>
+      <c r="C5" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
+        <v>334.37222222222215</v>
+      </c>
+      <c r="D5" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
+        <v>380.50555555555547</v>
+      </c>
+      <c r="E5" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
+        <v>341.56666666666666</v>
+      </c>
+      <c r="F5" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
+        <v>366.1444444444445</v>
+      </c>
+      <c r="G5" s="6">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
+        <v>310.35000000000002</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3">
+        <f>AVERAGE(C5:F5)</f>
+        <v>355.64722222222224</v>
+      </c>
+      <c r="J5" s="4" cm="1">
+        <f t="array" ref="J5">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A5))</f>
+        <v>73.808441403547434</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>150</v>
+      </c>
+      <c r="B6" s="6">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
+        <v>364.37222222222204</v>
+      </c>
+      <c r="C6" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
+        <v>384.11666666666667</v>
+      </c>
+      <c r="D6" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
+        <v>371.71111111111105</v>
+      </c>
+      <c r="E6" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
+        <v>449.72222222222217</v>
+      </c>
+      <c r="F6" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
+        <v>299.24444444444447</v>
+      </c>
+      <c r="G6" s="6">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
+        <v>353.84444444444443</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3">
+        <f t="shared" ref="I6:I8" si="1">AVERAGE(C6:F6)</f>
+        <v>376.19861111111112</v>
+      </c>
+      <c r="J6" s="4" cm="1">
+        <f t="array" ref="J6">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A6))</f>
+        <v>100.98374280994841</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>200</v>
+      </c>
+      <c r="B7" s="6">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
+        <v>359.87222222222215</v>
+      </c>
+      <c r="C7" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
+        <v>252.81111111111105</v>
+      </c>
+      <c r="D7" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
+        <v>334.13888888888891</v>
+      </c>
+      <c r="E7" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
+        <v>392.06666666666655</v>
+      </c>
+      <c r="F7" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
+        <v>333.29999999999995</v>
+      </c>
+      <c r="G7" s="6">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
+        <v>350.01666666666671</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3">
+        <f t="shared" si="1"/>
+        <v>328.07916666666659</v>
+      </c>
+      <c r="J7" s="4" cm="1">
+        <f t="array" ref="J7">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A7))</f>
+        <v>106.66357347130749</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>500</v>
+      </c>
+      <c r="B8" s="6">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
+        <v>384.7</v>
+      </c>
+      <c r="C8" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
+        <v>315.5</v>
+      </c>
+      <c r="D8" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
+        <v>332.1722222222221</v>
+      </c>
+      <c r="E8" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
+        <v>285.12777777777774</v>
+      </c>
+      <c r="F8" s="3">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
+        <v>358.63333333333327</v>
+      </c>
+      <c r="G8" s="6">
+        <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
+        <v>433.67777777777781</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3">
+        <f t="shared" si="1"/>
+        <v>322.85833333333329</v>
+      </c>
+      <c r="J8" s="4" cm="1">
+        <f t="array" ref="J8">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A8))</f>
+        <v>105.47308225273461</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>750</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="3"/>
+      <c r="I9">
+        <v>365.85</v>
+      </c>
+      <c r="J9" s="9">
+        <v>103.22199999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="6">
+        <f>AVERAGE(B5:B8)</f>
+        <v>366.22916666666657</v>
+      </c>
+      <c r="C11" s="3">
+        <f>AVERAGE(C5:C8)</f>
+        <v>321.69999999999993</v>
+      </c>
+      <c r="D11" s="3">
+        <f>AVERAGE(D5:D8)</f>
+        <v>354.63194444444434</v>
+      </c>
+      <c r="E11" s="3">
+        <f>AVERAGE(E5:E8)</f>
+        <v>367.12083333333328</v>
+      </c>
+      <c r="F11" s="3">
+        <f>AVERAGE(F5:F8)</f>
+        <v>339.33055555555552</v>
+      </c>
+      <c r="G11" s="6">
+        <f>AVERAGE(G5:G8)</f>
+        <v>361.97222222222229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="7" cm="1">
+        <f t="array" ref="B12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
+        <v>79.421143208516256</v>
+      </c>
+      <c r="C12" s="4" cm="1">
+        <f t="array" ref="C12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
+        <v>110.31819401678085</v>
+      </c>
+      <c r="D12" s="4" cm="1">
+        <f t="array" ref="D12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
+        <v>51.555768925847183</v>
+      </c>
+      <c r="E12" s="4" cm="1">
+        <f t="array" ref="E12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
+        <v>122.04853696977287</v>
+      </c>
+      <c r="F12" s="4" cm="1">
+        <f t="array" ref="F12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
+        <v>70.745885074933739</v>
+      </c>
+      <c r="G12" s="7" cm="1">
+        <f t="array" ref="G12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
+        <v>128.07988345739059</v>
+      </c>
+    </row>
+    <row r="19" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N19" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N34" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N50" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Experimenten4.xlsx
+++ b/Experimenten4.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="311" documentId="11_AA522F578FF748524973C9320039661620A74D1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B120E125-EBCF-4E0D-B3F3-24D7B0705CAF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1960" yWindow="1930" windowWidth="21600" windowHeight="11270" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alle experimenten" sheetId="1" r:id="rId1"/>
@@ -2293,7 +2293,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3E0E6033-A0FD-49EC-AC80-D988000F97A6}" type="CELLRANGE">
+                    <a:fld id="{2AD59433-2A8B-43B3-9FAA-DB1BFA11FA08}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2327,7 +2327,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{360AE5AB-B86B-4A54-BC1F-B542F45BB3D0}" type="CELLRANGE">
+                    <a:fld id="{D20ACA01-1978-43B2-8ED8-03B001A7B987}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2361,7 +2361,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{34660299-A55B-4096-B652-C64AD22F656D}" type="CELLRANGE">
+                    <a:fld id="{A737D3B8-6C91-48B4-BDEC-44BC850D73E9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2395,7 +2395,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6DB89E89-A74F-42B4-81C2-1942993A59FD}" type="CELLRANGE">
+                    <a:fld id="{8F056040-A1B6-4548-BFB5-4967A51E16FD}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2429,7 +2429,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{88DA0426-56C0-418C-992F-EF1A1510D282}" type="CELLRANGE">
+                    <a:fld id="{81DD8631-31CD-4D27-8F85-F904D8E16CD1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2463,7 +2463,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1BA6F217-5EEE-4C1B-85A7-B96E89B8CD2E}" type="CELLRANGE">
+                    <a:fld id="{F06A4C20-61AD-4888-935C-817FD2213C28}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3031,7 +3031,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C1B3A0DC-BEFE-4012-A010-167B628ACE00}" type="CELLRANGE">
+                    <a:fld id="{6CD0FADD-5DEB-48DC-91EE-A8BD3503DBF9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3065,7 +3065,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B6B3DC73-A616-41D8-816F-2413E5E8ECB7}" type="CELLRANGE">
+                    <a:fld id="{CB4D7558-7B8A-4B6C-8FA1-0D4E546A58E5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3099,7 +3099,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25E7426F-68D7-48A3-9758-B899E3E1523E}" type="CELLRANGE">
+                    <a:fld id="{2581BD5D-071F-4D37-A94F-35536417EAD1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3133,7 +3133,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AA0C8A97-DDAB-4919-8F6C-F8C5BD6C31BF}" type="CELLRANGE">
+                    <a:fld id="{892332AC-E79B-49D8-9FF8-2723C8F188A7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3167,7 +3167,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F9513D3B-BCE1-43FD-9A56-477A7A0004B1}" type="CELLRANGE">
+                    <a:fld id="{6AE363E1-3565-439A-A839-58D5924E73D2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3201,7 +3201,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1D3C9147-2673-417D-A0E7-F0D13BAF1979}" type="CELLRANGE">
+                    <a:fld id="{7D7397BE-99F7-4373-8857-06CBB6FF7506}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3756,7 +3756,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F034B9C6-57A6-4724-9268-C025B9CDECA6}" type="CELLRANGE">
+                    <a:fld id="{C2F03BB6-52EB-4A5A-AEAA-FF32661BCFE0}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3789,7 +3789,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AAFDCA52-015B-42C2-BF4B-8132C0F67D74}" type="CELLRANGE">
+                    <a:fld id="{69769136-85F2-4236-9204-60EF309F8A4B}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3823,7 +3823,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C5C45CF1-A84F-408F-B10A-F69D67EC5214}" type="CELLRANGE">
+                    <a:fld id="{9ED41710-01D7-4845-AC70-A177463DFA14}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3857,7 +3857,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BF9B62AD-956B-4C17-866E-978DD15A7EF1}" type="CELLRANGE">
+                    <a:fld id="{2243D590-82EC-4486-AFEA-ABBDC88E06C3}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3891,7 +3891,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{778779C7-E389-4837-A4AC-353503F054E5}" type="CELLRANGE">
+                    <a:fld id="{13D7BEDD-C939-4D0F-8DEB-980BF6177B59}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>

--- a/Experimenten4.xlsx
+++ b/Experimenten4.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="311" documentId="11_AA522F578FF748524973C9320039661620A74D1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B120E125-EBCF-4E0D-B3F3-24D7B0705CAF}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1960" yWindow="1930" windowWidth="21600" windowHeight="11270" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alle experimenten" sheetId="1" r:id="rId1"/>
@@ -2293,7 +2293,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2AD59433-2A8B-43B3-9FAA-DB1BFA11FA08}" type="CELLRANGE">
+                    <a:fld id="{5BCC5162-3852-43A0-85C3-E775A0BF5F31}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2327,7 +2327,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D20ACA01-1978-43B2-8ED8-03B001A7B987}" type="CELLRANGE">
+                    <a:fld id="{C8DE6D2C-091A-4BB8-BAD8-D8CA0B5EB974}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2361,7 +2361,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A737D3B8-6C91-48B4-BDEC-44BC850D73E9}" type="CELLRANGE">
+                    <a:fld id="{9FA32533-870A-4308-90AB-A32E9C920ACE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2395,7 +2395,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8F056040-A1B6-4548-BFB5-4967A51E16FD}" type="CELLRANGE">
+                    <a:fld id="{5731F93B-A81C-40EC-AFF7-47F235515776}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2429,7 +2429,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{81DD8631-31CD-4D27-8F85-F904D8E16CD1}" type="CELLRANGE">
+                    <a:fld id="{8CEDBAFB-3E2F-4938-9C1D-686BECD8A9B8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2463,7 +2463,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F06A4C20-61AD-4888-935C-817FD2213C28}" type="CELLRANGE">
+                    <a:fld id="{8DAC963D-E858-4365-93BC-F754335B77B2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3031,7 +3031,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6CD0FADD-5DEB-48DC-91EE-A8BD3503DBF9}" type="CELLRANGE">
+                    <a:fld id="{6022F07E-51A1-40D9-A96A-B0B2CB8CFBF4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3065,7 +3065,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CB4D7558-7B8A-4B6C-8FA1-0D4E546A58E5}" type="CELLRANGE">
+                    <a:fld id="{54F071F1-A7A3-4C74-B8EE-D3CD107BFDA5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3099,7 +3099,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2581BD5D-071F-4D37-A94F-35536417EAD1}" type="CELLRANGE">
+                    <a:fld id="{C90EF595-96F2-4F32-BB1B-9BFD6139945E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3133,7 +3133,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{892332AC-E79B-49D8-9FF8-2723C8F188A7}" type="CELLRANGE">
+                    <a:fld id="{428298F3-68BF-44E7-810F-B7D582232351}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3167,7 +3167,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6AE363E1-3565-439A-A839-58D5924E73D2}" type="CELLRANGE">
+                    <a:fld id="{96741391-6853-480F-B1ED-8A4D0F1AF7E5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3201,7 +3201,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7D7397BE-99F7-4373-8857-06CBB6FF7506}" type="CELLRANGE">
+                    <a:fld id="{BC75F835-DBF1-486B-A32C-2D6A581F915B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3756,7 +3756,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C2F03BB6-52EB-4A5A-AEAA-FF32661BCFE0}" type="CELLRANGE">
+                    <a:fld id="{71A77C1C-74F4-4936-BB2E-E8F3DB86B8AD}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3789,7 +3789,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{69769136-85F2-4236-9204-60EF309F8A4B}" type="CELLRANGE">
+                    <a:fld id="{3A07658B-97E5-433A-B0DA-DAAFAF06B382}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3823,7 +3823,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9ED41710-01D7-4845-AC70-A177463DFA14}" type="CELLRANGE">
+                    <a:fld id="{F22CAD7B-9F56-41FE-A08A-87E04CCE879B}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3857,7 +3857,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2243D590-82EC-4486-AFEA-ABBDC88E06C3}" type="CELLRANGE">
+                    <a:fld id="{A5FF0565-71CC-467F-AC04-ED083A85F08F}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3891,7 +3891,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{13D7BEDD-C939-4D0F-8DEB-980BF6177B59}" type="CELLRANGE">
+                    <a:fld id="{3774932A-0199-48AD-9E5A-F1BB343D1A98}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>

--- a/Experimenten4.xlsx
+++ b/Experimenten4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2810a0d4408f349/Documenten/GitHub/OR5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="11_AA522F578FF748524973C9320039661620A74D1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B120E125-EBCF-4E0D-B3F3-24D7B0705CAF}"/>
+  <xr:revisionPtr revIDLastSave="313" documentId="11_AA522F578FF748524973C9320039661620A74D1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36C3A96F-58D5-4A56-9A54-5C7149367C33}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alle experimenten" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -162,7 +162,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -219,17 +219,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="172" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -250,7 +248,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1204,7 +1202,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2194,7 +2192,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2312,7 +2310,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2346,7 +2343,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2380,7 +2376,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2414,7 +2409,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2448,7 +2442,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2482,7 +2475,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2932,7 +2924,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3050,7 +3042,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3084,7 +3075,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3118,7 +3108,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3152,7 +3141,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3186,7 +3174,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3220,7 +3207,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3657,7 +3643,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3789,7 +3775,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3A07658B-97E5-433A-B0DA-DAAFAF06B382}" type="CELLRANGE">
+                    <a:fld id="{8779F835-85E1-45C6-B90A-9C9D44929EDD}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3823,7 +3809,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F22CAD7B-9F56-41FE-A08A-87E04CCE879B}" type="CELLRANGE">
+                    <a:fld id="{EC21D5D1-713D-423B-9D8B-3708D5FC7C46}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3857,7 +3843,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A5FF0565-71CC-467F-AC04-ED083A85F08F}" type="CELLRANGE">
+                    <a:fld id="{BEEDBB73-57ED-4130-9402-444B3A267BF2}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3891,7 +3877,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3774932A-0199-48AD-9E5A-F1BB343D1A98}" type="CELLRANGE">
+                    <a:fld id="{5A6541D7-46D8-47A4-B32F-E63C510B7279}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7471,22 +7457,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K211"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.36328125" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7521,7 +7507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>70000</v>
       </c>
@@ -7556,7 +7542,7 @@
         <v>5.4862403999868548</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>70000</v>
       </c>
@@ -7591,7 +7577,7 @@
         <v>5.2879847000149311</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>70000</v>
       </c>
@@ -7626,7 +7612,7 @@
         <v>5.3286113000067417</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>70000</v>
       </c>
@@ -7661,7 +7647,7 @@
         <v>5.4278759000007986</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>70000</v>
       </c>
@@ -7696,7 +7682,7 @@
         <v>5.3958127999940189</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>70000</v>
       </c>
@@ -7731,7 +7717,7 @@
         <v>5.4214574999932674</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>70000</v>
       </c>
@@ -7766,7 +7752,7 @@
         <v>5.5024398000095971</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>70000</v>
       </c>
@@ -7801,7 +7787,7 @@
         <v>5.4252568999945652</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>70000</v>
       </c>
@@ -7836,7 +7822,7 @@
         <v>5.4009593999944627</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>70000</v>
       </c>
@@ -7871,7 +7857,7 @@
         <v>5.352932800000417</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>70000</v>
       </c>
@@ -7906,7 +7892,7 @@
         <v>5.4586825000005774</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>70000</v>
       </c>
@@ -7941,7 +7927,7 @@
         <v>5.3676586999936262</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>70000</v>
       </c>
@@ -7976,7 +7962,7 @@
         <v>5.4901777999912156</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>70000</v>
       </c>
@@ -8011,7 +7997,7 @@
         <v>5.4918017000018153</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>70000</v>
       </c>
@@ -8046,7 +8032,7 @@
         <v>5.4781649000069592</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>70000</v>
       </c>
@@ -8081,7 +8067,7 @@
         <v>5.4684198000177284</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>70000</v>
       </c>
@@ -8116,7 +8102,7 @@
         <v>5.3366022999980487</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>70000</v>
       </c>
@@ -8151,7 +8137,7 @@
         <v>5.4007717999920706</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>70000</v>
       </c>
@@ -8186,7 +8172,7 @@
         <v>5.6570938000077149</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>70000</v>
       </c>
@@ -8221,7 +8207,7 @@
         <v>5.4854627999884542</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>70000</v>
       </c>
@@ -8256,7 +8242,7 @@
         <v>5.5464021999941906</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>70000</v>
       </c>
@@ -8291,7 +8277,7 @@
         <v>5.3863133000122616</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>70000</v>
       </c>
@@ -8326,7 +8312,7 @@
         <v>5.4932814999920083</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>70000</v>
       </c>
@@ -8361,7 +8347,7 @@
         <v>5.4605587999976706</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>70000</v>
       </c>
@@ -8396,7 +8382,7 @@
         <v>5.6403131999977631</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>70000</v>
       </c>
@@ -8431,7 +8417,7 @@
         <v>5.3710718999936944</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>70000</v>
       </c>
@@ -8466,7 +8452,7 @@
         <v>5.8363017999945441</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>70000</v>
       </c>
@@ -8501,7 +8487,7 @@
         <v>5.993630499986466</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>70000</v>
       </c>
@@ -8536,7 +8522,7 @@
         <v>5.4403558000049088</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>70000</v>
       </c>
@@ -8571,7 +8557,7 @@
         <v>5.4401070000021718</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>70000</v>
       </c>
@@ -8606,7 +8592,7 @@
         <v>5.2861697000043932</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>70000</v>
       </c>
@@ -8641,7 +8627,7 @@
         <v>5.4719046999962302</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>70000</v>
       </c>
@@ -8676,7 +8662,7 @@
         <v>5.4979333000082988</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>70000</v>
       </c>
@@ -8711,7 +8697,7 @@
         <v>5.454824299988104</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>70000</v>
       </c>
@@ -8746,7 +8732,7 @@
         <v>5.6091917999874568</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>70000</v>
       </c>
@@ -8781,7 +8767,7 @@
         <v>5.4541254000214394</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>70000</v>
       </c>
@@ -8816,7 +8802,7 @@
         <v>5.4252436999959173</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>70000</v>
       </c>
@@ -8851,7 +8837,7 @@
         <v>5.4914328000013484</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>70000</v>
       </c>
@@ -8886,7 +8872,7 @@
         <v>5.4799296999844964</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>70000</v>
       </c>
@@ -8921,7 +8907,7 @@
         <v>5.4780500999913784</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>70000</v>
       </c>
@@ -8956,7 +8942,7 @@
         <v>5.5036676000017906</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>70000</v>
       </c>
@@ -8991,7 +8977,7 @@
         <v>5.4968678000004729</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>70000</v>
       </c>
@@ -9026,7 +9012,7 @@
         <v>5.5327691999991657</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>70000</v>
       </c>
@@ -9061,7 +9047,7 @@
         <v>5.6293098999885842</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>70000</v>
       </c>
@@ -9096,7 +9082,7 @@
         <v>5.4928616999968654</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>70000</v>
       </c>
@@ -9131,7 +9117,7 @@
         <v>5.3971242000116044</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>70000</v>
       </c>
@@ -9166,7 +9152,7 @@
         <v>5.5474619000015082</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>70000</v>
       </c>
@@ -9201,7 +9187,7 @@
         <v>5.6888022999919494</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>70000</v>
       </c>
@@ -9236,7 +9222,7 @@
         <v>5.4545953999913763</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>70000</v>
       </c>
@@ -9271,7 +9257,7 @@
         <v>5.5183144000038737</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>70000</v>
       </c>
@@ -9306,7 +9292,7 @@
         <v>5.4005103999952553</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>70000</v>
       </c>
@@ -9341,7 +9327,7 @@
         <v>5.441641699988395</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>70000</v>
       </c>
@@ -9376,7 +9362,7 @@
         <v>5.5560860999976276</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>70000</v>
       </c>
@@ -9411,7 +9397,7 @@
         <v>5.458142500006943</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>70000</v>
       </c>
@@ -9446,7 +9432,7 @@
         <v>5.4442836000089301</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>70000</v>
       </c>
@@ -9481,7 +9467,7 @@
         <v>5.4848492999881273</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>70000</v>
       </c>
@@ -9516,7 +9502,7 @@
         <v>5.4112370999937411</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>70000</v>
       </c>
@@ -9551,7 +9537,7 @@
         <v>5.5142770999955246</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>70000</v>
       </c>
@@ -9586,7 +9572,7 @@
         <v>5.5159693000023253</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>70000</v>
       </c>
@@ -9621,7 +9607,7 @@
         <v>5.4517025999957696</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>70000</v>
       </c>
@@ -9656,7 +9642,7 @@
         <v>5.383823800002574</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>70000</v>
       </c>
@@ -9691,12 +9677,12 @@
         <v>5.5494637999945553</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>70000</v>
       </c>
       <c r="B64">
-        <v>0.99344277847092743</v>
+        <v>0.99344277847092699</v>
       </c>
       <c r="C64">
         <v>100</v>
@@ -9726,7 +9712,7 @@
         <v>5.2907038999983342</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>70000</v>
       </c>
@@ -9761,7 +9747,7 @@
         <v>5.3541529000067376</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>70000</v>
       </c>
@@ -9796,7 +9782,7 @@
         <v>5.2348554999916814</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>70000</v>
       </c>
@@ -9831,7 +9817,7 @@
         <v>5.5762047999887727</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>70000</v>
       </c>
@@ -9866,7 +9852,7 @@
         <v>5.4850226000125986</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>70000</v>
       </c>
@@ -9901,7 +9887,7 @@
         <v>5.5608098000084283</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>70000</v>
       </c>
@@ -9936,7 +9922,7 @@
         <v>5.4910147000045981</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70000</v>
       </c>
@@ -9971,7 +9957,7 @@
         <v>5.4554984999995213</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70000</v>
       </c>
@@ -10006,7 +9992,7 @@
         <v>5.4882175000093412</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70000</v>
       </c>
@@ -10041,7 +10027,7 @@
         <v>5.4942360000131876</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>70000</v>
       </c>
@@ -10076,7 +10062,7 @@
         <v>5.6580567999917548</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>70000</v>
       </c>
@@ -10111,7 +10097,7 @@
         <v>5.4267287999973632</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>70000</v>
       </c>
@@ -10146,7 +10132,7 @@
         <v>5.4175782000093022</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>70000</v>
       </c>
@@ -10181,7 +10167,7 @@
         <v>5.5764956999919377</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>70000</v>
       </c>
@@ -10216,7 +10202,7 @@
         <v>5.5175904999923659</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>70000</v>
       </c>
@@ -10251,7 +10237,7 @@
         <v>5.5198772999865469</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>70000</v>
       </c>
@@ -10286,7 +10272,7 @@
         <v>5.5172108999977354</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>70000</v>
       </c>
@@ -10321,7 +10307,7 @@
         <v>5.3989683999971021</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>70000</v>
       </c>
@@ -10356,7 +10342,7 @@
         <v>5.5347767999919597</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>70000</v>
       </c>
@@ -10391,7 +10377,7 @@
         <v>5.6479407000151696</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>70000</v>
       </c>
@@ -10426,7 +10412,7 @@
         <v>5.4130385000025854</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>70000</v>
       </c>
@@ -10461,7 +10447,7 @@
         <v>5.4161419000156457</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>70000</v>
       </c>
@@ -10496,7 +10482,7 @@
         <v>5.4464356000098633</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>70000</v>
       </c>
@@ -10531,7 +10517,7 @@
         <v>5.6166250000096616</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>70000</v>
       </c>
@@ -10566,7 +10552,7 @@
         <v>5.5304822000034619</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>70000</v>
       </c>
@@ -10601,7 +10587,7 @@
         <v>5.5718799000023864</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>70000</v>
       </c>
@@ -10636,7 +10622,7 @@
         <v>5.5633484999852953</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>70000</v>
       </c>
@@ -10671,7 +10657,7 @@
         <v>5.5850031000009039</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>70000</v>
       </c>
@@ -10706,7 +10692,7 @@
         <v>5.5347347000060836</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>70000</v>
       </c>
@@ -10741,7 +10727,7 @@
         <v>5.3718701000034343</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>70000</v>
       </c>
@@ -10776,7 +10762,7 @@
         <v>5.503811599992332</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>70000</v>
       </c>
@@ -10811,7 +10797,7 @@
         <v>5.4048397000005934</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>70000</v>
       </c>
@@ -10846,7 +10832,7 @@
         <v>5.3995544999925187</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>70000</v>
       </c>
@@ -10881,7 +10867,7 @@
         <v>5.5285912999970606</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>70000</v>
       </c>
@@ -10916,7 +10902,7 @@
         <v>5.4736036000103923</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>70000</v>
       </c>
@@ -10951,7 +10937,7 @@
         <v>5.5013610000023618</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>70000</v>
       </c>
@@ -10986,7 +10972,7 @@
         <v>5.4882464999973308</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>70000</v>
       </c>
@@ -11021,7 +11007,7 @@
         <v>5.5281380000087674</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>70000</v>
       </c>
@@ -11056,7 +11042,7 @@
         <v>5.4136193999875104</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>70000</v>
       </c>
@@ -11091,7 +11077,7 @@
         <v>5.617174500002875</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>70000</v>
       </c>
@@ -11126,7 +11112,7 @@
         <v>5.5348951000196394</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>70000</v>
       </c>
@@ -11161,7 +11147,7 @@
         <v>5.5336121999862371</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>70000</v>
       </c>
@@ -11196,7 +11182,7 @@
         <v>5.5184537000022829</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>70000</v>
       </c>
@@ -11231,7 +11217,7 @@
         <v>5.7365925000049174</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>70000</v>
       </c>
@@ -11266,7 +11252,7 @@
         <v>5.4973973999876762</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>70000</v>
       </c>
@@ -11301,7 +11287,7 @@
         <v>5.4988298999960534</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>70000</v>
       </c>
@@ -11336,7 +11322,7 @@
         <v>5.5905288999929326</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>70000</v>
       </c>
@@ -11371,7 +11357,7 @@
         <v>5.4938764999969862</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>70000</v>
       </c>
@@ -11406,7 +11392,7 @@
         <v>5.3953062999935364</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>70000</v>
       </c>
@@ -11441,7 +11427,7 @@
         <v>5.6602434999949756</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>70000</v>
       </c>
@@ -11476,7 +11462,7 @@
         <v>5.6454630000080206</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>70000</v>
       </c>
@@ -11511,7 +11497,7 @@
         <v>5.5846527999965474</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>70000</v>
       </c>
@@ -11546,7 +11532,7 @@
         <v>5.5755204999877606</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>70000</v>
       </c>
@@ -11581,7 +11567,7 @@
         <v>5.6009620999975596</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>70000</v>
       </c>
@@ -11616,7 +11602,7 @@
         <v>5.6116392999974778</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>70000</v>
       </c>
@@ -11651,7 +11637,7 @@
         <v>5.5959707000001799</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>70000</v>
       </c>
@@ -11686,7 +11672,7 @@
         <v>5.6165087999979733</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>70000</v>
       </c>
@@ -11721,7 +11707,7 @@
         <v>5.6554116999905091</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>70000</v>
       </c>
@@ -11756,7 +11742,7 @@
         <v>5.4286443000019062</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>70000</v>
       </c>
@@ -11791,7 +11777,7 @@
         <v>5.4205696999997599</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>70000</v>
       </c>
@@ -11826,7 +11812,7 @@
         <v>5.3985808999859728</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>70000</v>
       </c>
@@ -11861,7 +11847,7 @@
         <v>5.3885965999943437</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>70000</v>
       </c>
@@ -11896,7 +11882,7 @@
         <v>5.5135240000090562</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>70000</v>
       </c>
@@ -11931,7 +11917,7 @@
         <v>5.6957664000074146</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>70000</v>
       </c>
@@ -11966,7 +11952,7 @@
         <v>5.6080256000132067</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>70000</v>
       </c>
@@ -12001,7 +11987,7 @@
         <v>5.7904736999917077</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>70000</v>
       </c>
@@ -12036,7 +12022,7 @@
         <v>5.4898987999913524</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>70000</v>
       </c>
@@ -12071,7 +12057,7 @@
         <v>5.5945358000026317</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>70000</v>
       </c>
@@ -12106,7 +12092,7 @@
         <v>5.5469640000083018</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>70000</v>
       </c>
@@ -12141,7 +12127,7 @@
         <v>5.4908743999985754</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>70000</v>
       </c>
@@ -12176,7 +12162,7 @@
         <v>5.5923691999923903</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>70000</v>
       </c>
@@ -12211,7 +12197,7 @@
         <v>5.632353900000453</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>70000</v>
       </c>
@@ -12246,7 +12232,7 @@
         <v>5.3709352999867406</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>70000</v>
       </c>
@@ -12281,7 +12267,7 @@
         <v>5.6315172999893548</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>70000</v>
       </c>
@@ -12316,7 +12302,7 @@
         <v>5.5436397000012221</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>70000</v>
       </c>
@@ -12351,7 +12337,7 @@
         <v>5.6179967000061879</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>70000</v>
       </c>
@@ -12386,7 +12372,7 @@
         <v>5.5271779999893624</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>70000</v>
       </c>
@@ -12421,7 +12407,7 @@
         <v>5.4870652999961749</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>70000</v>
       </c>
@@ -12456,7 +12442,7 @@
         <v>5.6252593999961391</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>70000</v>
       </c>
@@ -12491,7 +12477,7 @@
         <v>5.609474400000181</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>70000</v>
       </c>
@@ -12526,7 +12512,7 @@
         <v>5.5344228999892948</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>70000</v>
       </c>
@@ -12561,7 +12547,7 @@
         <v>5.66388820001157</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>70000</v>
       </c>
@@ -12596,7 +12582,7 @@
         <v>5.6976474000111921</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>70000</v>
       </c>
@@ -12631,7 +12617,7 @@
         <v>5.483169099999941</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>70000</v>
       </c>
@@ -12666,7 +12652,7 @@
         <v>5.6228725999972076</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>70000</v>
       </c>
@@ -12701,7 +12687,7 @@
         <v>5.5762456999946153</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>70000</v>
       </c>
@@ -12736,7 +12722,7 @@
         <v>5.6415805999859003</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>70000</v>
       </c>
@@ -12771,7 +12757,7 @@
         <v>5.4804294000059599</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>70000</v>
       </c>
@@ -12806,7 +12792,7 @@
         <v>5.3574181000003591</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>70000</v>
       </c>
@@ -12841,7 +12827,7 @@
         <v>5.3712397999915993</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>70000</v>
       </c>
@@ -12876,7 +12862,7 @@
         <v>5.4004716000054032</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>70000</v>
       </c>
@@ -12911,7 +12897,7 @@
         <v>5.3194586999888998</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>70000</v>
       </c>
@@ -12946,7 +12932,7 @@
         <v>5.6496053999871947</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>70000</v>
       </c>
@@ -12981,7 +12967,7 @@
         <v>5.5344863999926019</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>70000</v>
       </c>
@@ -13016,7 +13002,7 @@
         <v>5.5536712000030093</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>70000</v>
       </c>
@@ -13051,7 +13037,7 @@
         <v>5.5071129000134533</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>70000</v>
       </c>
@@ -13086,7 +13072,7 @@
         <v>5.5292266000033123</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>70000</v>
       </c>
@@ -13121,7 +13107,7 @@
         <v>5.4909938999917358</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>70000</v>
       </c>
@@ -13156,7 +13142,7 @@
         <v>5.5465432000055443</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>70000</v>
       </c>
@@ -13191,7 +13177,7 @@
         <v>5.4590059999900404</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>70000</v>
       </c>
@@ -13226,7 +13212,7 @@
         <v>5.4736427000170806</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>70000</v>
       </c>
@@ -13261,7 +13247,7 @@
         <v>5.9256452000117861</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>70000</v>
       </c>
@@ -13296,7 +13282,7 @@
         <v>8.7022127999953227</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>70000</v>
       </c>
@@ -13331,7 +13317,7 @@
         <v>7.5487007000047024</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>70000</v>
       </c>
@@ -13366,7 +13352,7 @@
         <v>5.7690268000005744</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>70000</v>
       </c>
@@ -13401,7 +13387,7 @@
         <v>5.1563337999978103</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>70000</v>
       </c>
@@ -13436,7 +13422,7 @@
         <v>5.1824070000002393</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>70000</v>
       </c>
@@ -13471,7 +13457,7 @@
         <v>6.3845861000008881</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>70000</v>
       </c>
@@ -13506,7 +13492,7 @@
         <v>5.1972315000020899</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>70000</v>
       </c>
@@ -13541,7 +13527,7 @@
         <v>4.7006769999861717</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>70000</v>
       </c>
@@ -13576,7 +13562,7 @@
         <v>4.5645587999897543</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>70000</v>
       </c>
@@ -13611,7 +13597,7 @@
         <v>4.5141120000043884</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>70000</v>
       </c>
@@ -13646,7 +13632,7 @@
         <v>4.864603400012129</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>70000</v>
       </c>
@@ -13681,7 +13667,7 @@
         <v>4.4946021000068868</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>70000</v>
       </c>
@@ -13716,7 +13702,7 @@
         <v>4.5765301000210457</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>70000</v>
       </c>
@@ -13751,7 +13737,7 @@
         <v>4.6624580000061542</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>70000</v>
       </c>
@@ -13786,7 +13772,7 @@
         <v>4.5590339000045788</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>70000</v>
       </c>
@@ -13821,7 +13807,7 @@
         <v>5.2118497000046773</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>70000</v>
       </c>
@@ -13856,7 +13842,7 @@
         <v>4.8484873000124944</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>70000</v>
       </c>
@@ -13891,7 +13877,7 @@
         <v>4.5169654000201263</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>70000</v>
       </c>
@@ -13926,7 +13912,7 @@
         <v>4.6380415999883553</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>70000</v>
       </c>
@@ -13961,7 +13947,7 @@
         <v>4.6955578999913996</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>70000</v>
       </c>
@@ -13996,7 +13982,7 @@
         <v>4.5501588999904934</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>70000</v>
       </c>
@@ -14031,7 +14017,7 @@
         <v>4.5285080999892671</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>70000</v>
       </c>
@@ -14066,7 +14052,7 @@
         <v>4.5849701999977697</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>70000</v>
       </c>
@@ -14101,7 +14087,7 @@
         <v>4.7370612999948207</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>70000</v>
       </c>
@@ -14136,7 +14122,7 @@
         <v>4.6931349999940721</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>70000</v>
       </c>
@@ -14171,7 +14157,7 @@
         <v>4.5657396000169683</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>70000</v>
       </c>
@@ -14206,7 +14192,7 @@
         <v>4.6579338999872562</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>70000</v>
       </c>
@@ -14241,7 +14227,7 @@
         <v>4.8646519999892917</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>70000</v>
       </c>
@@ -14276,7 +14262,7 @@
         <v>5.261319099998218</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>70000</v>
       </c>
@@ -14311,7 +14297,7 @@
         <v>5.0402452999987872</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>70000</v>
       </c>
@@ -14346,7 +14332,7 @@
         <v>5.3113833999959752</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>70000</v>
       </c>
@@ -14381,7 +14367,7 @@
         <v>4.628458999999566</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>70000</v>
       </c>
@@ -14416,7 +14402,7 @@
         <v>4.6917124000028707</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>70000</v>
       </c>
@@ -14451,7 +14437,7 @@
         <v>4.6777011999947717</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>70000</v>
       </c>
@@ -14486,7 +14472,7 @@
         <v>4.6111103000148432</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>70000</v>
       </c>
@@ -14521,7 +14507,7 @@
         <v>4.7697809999954188</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>70000</v>
       </c>
@@ -14556,7 +14542,7 @@
         <v>4.8671342999878107</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>70000</v>
       </c>
@@ -14591,7 +14577,7 @@
         <v>5.1215529999899454</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>70000</v>
       </c>
@@ -14626,7 +14612,7 @@
         <v>4.5786801999929594</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>70000</v>
       </c>
@@ -14661,7 +14647,7 @@
         <v>4.4873394000169364</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>70000</v>
       </c>
@@ -14696,7 +14682,7 @@
         <v>4.3980791999929352</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>70000</v>
       </c>
@@ -14731,7 +14717,7 @@
         <v>4.4200246999971569</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>70000</v>
       </c>
@@ -14766,7 +14752,7 @@
         <v>4.4822079000005033</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>70000</v>
       </c>
@@ -14801,7 +14787,7 @@
         <v>4.4898767999984557</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>70000</v>
       </c>
@@ -14836,7 +14822,7 @@
         <v>4.4411232999991634</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>70000</v>
       </c>
@@ -14879,18 +14865,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -14913,7 +14899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>50</v>
       </c>
@@ -14936,7 +14922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>50</v>
       </c>
@@ -14959,7 +14945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>50</v>
       </c>
@@ -14982,7 +14968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>50</v>
       </c>
@@ -15005,7 +14991,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>50</v>
       </c>
@@ -15028,7 +15014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>50</v>
       </c>
@@ -15051,7 +15037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>80</v>
       </c>
@@ -15074,7 +15060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>80</v>
       </c>
@@ -15097,7 +15083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>80</v>
       </c>
@@ -15120,7 +15106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>80</v>
       </c>
@@ -15143,7 +15129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>80</v>
       </c>
@@ -15166,7 +15152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>80</v>
       </c>
@@ -15189,7 +15175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>100</v>
       </c>
@@ -15200,7 +15186,7 @@
         <v>390.74999999999989</v>
       </c>
       <c r="D14">
-        <v>146.0555555555556</v>
+        <v>146.055555555556</v>
       </c>
       <c r="E14">
         <v>230.11671589021671</v>
@@ -15212,7 +15198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>100</v>
       </c>
@@ -15235,7 +15221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>100</v>
       </c>
@@ -15258,7 +15244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>100</v>
       </c>
@@ -15281,7 +15267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>100</v>
       </c>
@@ -15304,7 +15290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>100</v>
       </c>
@@ -15327,7 +15313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>120</v>
       </c>
@@ -15350,7 +15336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>120</v>
       </c>
@@ -15373,7 +15359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>120</v>
       </c>
@@ -15396,7 +15382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>120</v>
       </c>
@@ -15419,7 +15405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>120</v>
       </c>
@@ -15442,7 +15428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>120</v>
       </c>
@@ -15465,7 +15451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>150</v>
       </c>
@@ -15488,7 +15474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>150</v>
       </c>
@@ -15511,7 +15497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>150</v>
       </c>
@@ -15534,7 +15520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>150</v>
       </c>
@@ -15557,7 +15543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>150</v>
       </c>
@@ -15580,7 +15566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>150</v>
       </c>
@@ -15603,7 +15589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>200</v>
       </c>
@@ -15626,7 +15612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>200</v>
       </c>
@@ -15649,7 +15635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>200</v>
       </c>
@@ -15672,7 +15658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>200</v>
       </c>
@@ -15695,7 +15681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>200</v>
       </c>
@@ -15718,7 +15704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>200</v>
       </c>
@@ -15741,7 +15727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>500</v>
       </c>
@@ -15764,7 +15750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>500</v>
       </c>
@@ -15787,7 +15773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>500</v>
       </c>
@@ -15810,7 +15796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>500</v>
       </c>
@@ -15833,7 +15819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>500</v>
       </c>
@@ -15856,7 +15842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>500</v>
       </c>
@@ -15887,14 +15873,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E265F2D-4BDB-4332-91AD-88FABCDE77F4}">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -15917,7 +15903,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>50</v>
       </c>
@@ -15950,7 +15936,7 @@
         <v>525.25370370370365</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>80</v>
       </c>
@@ -15983,7 +15969,7 @@
         <v>370.11018518518512</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>100</v>
       </c>
@@ -16016,7 +16002,7 @@
         <v>364.9175925925926</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>120</v>
       </c>
@@ -16049,7 +16035,7 @@
         <v>337.22222222222223</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>150</v>
       </c>
@@ -16082,7 +16068,7 @@
         <v>363.35092592592588</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>200</v>
       </c>
@@ -16115,7 +16101,7 @@
         <v>330.38425925925918</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>500</v>
       </c>
@@ -16148,7 +16134,7 @@
         <v>347.58518518518514</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10">
         <f>AVERAGE(B2:B8)</f>
         <v>388.05238095238076</v>
@@ -16183,9 +16169,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -16208,7 +16194,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>50</v>
       </c>
@@ -16231,7 +16217,7 @@
         <v>361.72222222222217</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>80</v>
       </c>
@@ -16254,7 +16240,7 @@
         <v>340.91111111111121</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>100</v>
       </c>
@@ -16277,7 +16263,7 @@
         <v>313.8555555555555</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>120</v>
       </c>
@@ -16300,7 +16286,7 @@
         <v>305.91666666666669</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>150</v>
       </c>
@@ -16323,7 +16309,7 @@
         <v>353.51111111111112</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>200</v>
       </c>
@@ -16346,7 +16332,7 @@
         <v>350.01666666666671</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>500</v>
       </c>
@@ -16377,50 +16363,49 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD075B78-C560-45B4-82DD-6832EAF8A444}">
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>25</v>
       </c>
       <c r="N1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>50</v>
       </c>
@@ -16448,13 +16433,11 @@
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A2,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
         <v>362.92222222222222</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>80</v>
       </c>
@@ -16487,12 +16470,12 @@
         <f>AVERAGE(C3:G3)</f>
         <v>365.8533333333333</v>
       </c>
-      <c r="J3" s="5" cm="1">
+      <c r="J3" s="4" cm="1">
         <f t="array" ref="J3">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A3))</f>
         <v>101.25638696181393</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>100</v>
       </c>
@@ -16525,257 +16508,246 @@
         <f t="shared" ref="I4" si="0">AVERAGE(C4:G4)</f>
         <v>361.03111111111104</v>
       </c>
-      <c r="J4" s="5" cm="1">
+      <c r="J4" s="4" cm="1">
         <f t="array" ref="J4">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A4))</f>
         <v>116.72029457180238</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>120</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
         <v>355.97222222222223</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
         <v>334.37222222222215</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
         <v>380.50555555555547</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
         <v>341.56666666666666</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
         <v>366.1444444444445</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A5,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
         <v>310.35000000000002</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3">
+      <c r="I5">
         <f>AVERAGE(C5:F5)</f>
         <v>355.64722222222224</v>
       </c>
-      <c r="J5" s="4" cm="1">
+      <c r="J5" s="3" cm="1">
         <f t="array" ref="J5">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A5))</f>
         <v>73.808441403547434</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>150</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
         <v>364.37222222222204</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
         <v>384.11666666666667</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
         <v>371.71111111111105</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
         <v>449.72222222222217</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
         <v>299.24444444444447</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A6,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
         <v>353.84444444444443</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3">
+      <c r="I6">
         <f t="shared" ref="I6:I8" si="1">AVERAGE(C6:F6)</f>
         <v>376.19861111111112</v>
       </c>
-      <c r="J6" s="4" cm="1">
+      <c r="J6" s="3" cm="1">
         <f t="array" ref="J6">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A6))</f>
         <v>100.98374280994841</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>200</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
         <v>359.87222222222215</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
         <v>252.81111111111105</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
         <v>334.13888888888891</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
         <v>392.06666666666655</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
         <v>333.29999999999995</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A7,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
         <v>350.01666666666671</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3">
+      <c r="I7">
         <f t="shared" si="1"/>
         <v>328.07916666666659</v>
       </c>
-      <c r="J7" s="4" cm="1">
+      <c r="J7" s="3" cm="1">
         <f t="array" ref="J7">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A7))</f>
         <v>106.66357347130749</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>500</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))</f>
         <v>384.7</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))</f>
         <v>315.5</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))</f>
         <v>332.1722222222221</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))</f>
         <v>285.12777777777774</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))</f>
         <v>358.63333333333327</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <f>AVERAGEIFS('Alle experimenten'!$F:$F,'Alle experimenten'!$D:$D,$A8,'Alle experimenten'!$C:$C,VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))</f>
         <v>433.67777777777781</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3">
+      <c r="I8">
         <f t="shared" si="1"/>
         <v>322.85833333333329</v>
       </c>
-      <c r="J8" s="4" cm="1">
+      <c r="J8" s="3" cm="1">
         <f t="array" ref="J8">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,'Alle experimenten'!$D$2:$D$1000=A8))</f>
         <v>105.47308225273461</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>750</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="3"/>
+      <c r="B9" s="5"/>
+      <c r="G9" s="5"/>
       <c r="I9">
         <v>365.85</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="3">
         <v>103.22199999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="6">
-        <f>AVERAGE(B5:B8)</f>
+      <c r="B11" s="5">
+        <f t="shared" ref="B11:G11" si="2">AVERAGE(B5:B8)</f>
         <v>366.22916666666657</v>
       </c>
-      <c r="C11" s="3">
-        <f>AVERAGE(C5:C8)</f>
+      <c r="C11">
+        <f t="shared" si="2"/>
         <v>321.69999999999993</v>
       </c>
-      <c r="D11" s="3">
-        <f>AVERAGE(D5:D8)</f>
+      <c r="D11">
+        <f t="shared" si="2"/>
         <v>354.63194444444434</v>
       </c>
-      <c r="E11" s="3">
-        <f>AVERAGE(E5:E8)</f>
+      <c r="E11">
+        <f t="shared" si="2"/>
         <v>367.12083333333328</v>
       </c>
-      <c r="F11" s="3">
-        <f>AVERAGE(F5:F8)</f>
+      <c r="F11">
+        <f t="shared" si="2"/>
         <v>339.33055555555552</v>
       </c>
-      <c r="G11" s="6">
-        <f>AVERAGE(G5:G8)</f>
+      <c r="G11" s="5">
+        <f t="shared" si="2"/>
         <v>361.97222222222229</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="7" cm="1">
+      <c r="B12" s="6" cm="1">
         <f t="array" ref="B12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(B$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
         <v>79.421143208516256</v>
       </c>
-      <c r="C12" s="4" cm="1">
+      <c r="C12" s="3" cm="1">
         <f t="array" ref="C12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(C$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
         <v>110.31819401678085</v>
       </c>
-      <c r="D12" s="4" cm="1">
+      <c r="D12" s="3" cm="1">
         <f t="array" ref="D12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(D$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
         <v>51.555768925847183</v>
       </c>
-      <c r="E12" s="4" cm="1">
+      <c r="E12" s="3" cm="1">
         <f t="array" ref="E12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(E$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
         <v>122.04853696977287</v>
       </c>
-      <c r="F12" s="4" cm="1">
+      <c r="F12" s="3" cm="1">
         <f t="array" ref="F12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(F$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
         <v>70.745885074933739</v>
       </c>
-      <c r="G12" s="7" cm="1">
+      <c r="G12" s="6" cm="1">
         <f t="array" ref="G12">_xlfn.STDEV.S(_xlfn._xlws.FILTER('Alle experimenten'!$F$2:$F$1000,('Alle experimenten'!$C$2:$C$1000=VALUE(TRIM(_xlfn.TEXTAFTER(G$1,"="))))*('Alle experimenten'!$D$2:$D$1000&gt;=120)))</f>
         <v>128.07988345739059</v>
       </c>
     </row>
-    <row r="19" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N19" s="8" t="s">
+    <row r="19" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N19" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N34" s="8" t="s">
+    <row r="34" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N34" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N50" s="8" t="s">
+    <row r="50" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N50" s="7" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Experimenten4.xlsx
+++ b/Experimenten4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="11_AA522F578FF748524973C9320039661620A74D1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36C3A96F-58D5-4A56-9A54-5C7149367C33}"/>
+  <xr:revisionPtr revIDLastSave="314" documentId="11_AA522F578FF748524973C9320039661620A74D1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C91397C-68F2-415F-B0D7-6F9E5DC0D2CB}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alle experimenten" sheetId="1" r:id="rId1"/>
@@ -3775,7 +3775,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8779F835-85E1-45C6-B90A-9C9D44929EDD}" type="CELLRANGE">
+                    <a:fld id="{F9640E31-182A-4423-80C6-5947EA081D96}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3809,7 +3809,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EC21D5D1-713D-423B-9D8B-3708D5FC7C46}" type="CELLRANGE">
+                    <a:fld id="{E1F29077-23D7-4537-BCDA-B749E12473B1}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3843,7 +3843,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BEEDBB73-57ED-4130-9402-444B3A267BF2}" type="CELLRANGE">
+                    <a:fld id="{3B0513BA-D93F-4CB5-B4AA-4333FB71B721}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3877,7 +3877,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5A6541D7-46D8-47A4-B32F-E63C510B7279}" type="CELLRANGE">
+                    <a:fld id="{05C88AC9-1B0A-4054-A425-E5E7EFA1E1EC}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9678,37 +9678,37 @@
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>70000</v>
-      </c>
-      <c r="B64">
+      <c r="A64" s="1">
+        <v>70000</v>
+      </c>
+      <c r="B64" s="1">
         <v>0.99344277847092699</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="1">
         <v>100</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
         <v>100</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="1">
         <v>14</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="1">
         <v>146.0555555555556</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="1">
         <v>146.0555555555556</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="1">
         <v>16.972222222222229</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="1">
         <v>5.2576173999987077</v>
       </c>
-      <c r="J64">
+      <c r="J64" s="1">
         <v>3.308649999962654E-2</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="1">
         <v>5.2907038999983342</v>
       </c>
     </row>

--- a/Experimenten4.xlsx
+++ b/Experimenten4.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="314" documentId="11_AA522F578FF748524973C9320039661620A74D1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C91397C-68F2-415F-B0D7-6F9E5DC0D2CB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alle experimenten" sheetId="1" r:id="rId1"/>
@@ -3775,7 +3775,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F9640E31-182A-4423-80C6-5947EA081D96}" type="CELLRANGE">
+                    <a:fld id="{4772A753-6497-4435-98CE-6C5E2B0261D9}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3809,7 +3809,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E1F29077-23D7-4537-BCDA-B749E12473B1}" type="CELLRANGE">
+                    <a:fld id="{88AE5C5E-4246-47C3-9532-2365F202EDA1}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3843,7 +3843,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3B0513BA-D93F-4CB5-B4AA-4333FB71B721}" type="CELLRANGE">
+                    <a:fld id="{C861FC5F-44E6-47F2-906A-C1FA5E4E7114}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3877,7 +3877,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{05C88AC9-1B0A-4054-A425-E5E7EFA1E1EC}" type="CELLRANGE">
+                    <a:fld id="{87C1D4D9-E43B-4BF9-94BC-3FAFED7F881F}" type="CELLRANGE">
                       <a:rPr lang="nl-NL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7457,22 +7457,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K211"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>70000</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>5.4862403999868548</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>70000</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>5.2879847000149311</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>70000</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>5.3286113000067417</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>70000</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>5.4278759000007986</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>70000</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>5.3958127999940189</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>70000</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>5.4214574999932674</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>70000</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>5.5024398000095971</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>70000</v>
       </c>
@@ -7787,7 +7787,7 @@
         <v>5.4252568999945652</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>70000</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>5.4009593999944627</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>70000</v>
       </c>
@@ -7857,7 +7857,7 @@
         <v>5.352932800000417</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>70000</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>5.4586825000005774</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>70000</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>5.3676586999936262</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>70000</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>5.4901777999912156</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>70000</v>
       </c>
@@ -7997,7 +7997,7 @@
         <v>5.4918017000018153</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>70000</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>5.4781649000069592</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>70000</v>
       </c>
@@ -8067,7 +8067,7 @@
         <v>5.4684198000177284</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>70000</v>
       </c>
@@ -8102,7 +8102,7 @@
         <v>5.3366022999980487</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>70000</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>5.4007717999920706</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>70000</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>5.6570938000077149</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>70000</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>5.4854627999884542</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>70000</v>
       </c>
@@ -8242,7 +8242,7 @@
         <v>5.5464021999941906</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>70000</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>5.3863133000122616</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>70000</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>5.4932814999920083</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>70000</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>5.4605587999976706</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>70000</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>5.6403131999977631</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>70000</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>5.3710718999936944</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>70000</v>
       </c>
@@ -8452,7 +8452,7 @@
         <v>5.8363017999945441</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>70000</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>5.993630499986466</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>70000</v>
       </c>
@@ -8522,7 +8522,7 @@
         <v>5.4403558000049088</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>70000</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>5.4401070000021718</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>70000</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>5.2861697000043932</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>70000</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>5.4719046999962302</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>70000</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>5.4979333000082988</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>70000</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>5.454824299988104</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>70000</v>
       </c>
@@ -8732,7 +8732,7 @@
         <v>5.6091917999874568</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>70000</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>5.4541254000214394</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>70000</v>
       </c>
@@ -8802,7 +8802,7 @@
         <v>5.4252436999959173</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>70000</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>5.4914328000013484</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>70000</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>5.4799296999844964</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>70000</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>5.4780500999913784</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>70000</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>5.5036676000017906</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>70000</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>5.4968678000004729</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>70000</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>5.5327691999991657</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>70000</v>
       </c>
@@ -9047,7 +9047,7 @@
         <v>5.6293098999885842</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>70000</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>5.4928616999968654</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>70000</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>5.3971242000116044</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>70000</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>5.5474619000015082</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>70000</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>5.6888022999919494</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>70000</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>5.4545953999913763</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>70000</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>5.5183144000038737</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>70000</v>
       </c>
@@ -9292,7 +9292,7 @@
         <v>5.4005103999952553</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>70000</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>5.441641699988395</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>70000</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>5.5560860999976276</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>70000</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>5.458142500006943</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>70000</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>5.4442836000089301</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>70000</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>5.4848492999881273</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>70000</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>5.4112370999937411</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>70000</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>5.5142770999955246</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>70000</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>5.5159693000023253</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>70000</v>
       </c>
@@ -9607,7 +9607,7 @@
         <v>5.4517025999957696</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>70000</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>5.383823800002574</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>70000</v>
       </c>
@@ -9677,7 +9677,7 @@
         <v>5.5494637999945553</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>70000</v>
       </c>
@@ -9712,7 +9712,7 @@
         <v>5.2907038999983342</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>70000</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>5.3541529000067376</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>70000</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>5.2348554999916814</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>70000</v>
       </c>
@@ -9817,7 +9817,7 @@
         <v>5.5762047999887727</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>70000</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>5.4850226000125986</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>70000</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>5.5608098000084283</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>70000</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>5.4910147000045981</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70000</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>5.4554984999995213</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>70000</v>
       </c>
@@ -9992,7 +9992,7 @@
         <v>5.4882175000093412</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>70000</v>
       </c>
@@ -10027,7 +10027,7 @@
         <v>5.4942360000131876</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>70000</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>5.6580567999917548</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>70000</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>5.4267287999973632</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>70000</v>
       </c>
@@ -10132,7 +10132,7 @@
         <v>5.4175782000093022</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>70000</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>5.5764956999919377</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>70000</v>
       </c>
@@ -10202,7 +10202,7 @@
         <v>5.5175904999923659</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>70000</v>
       </c>
@@ -10237,7 +10237,7 @@
         <v>5.5198772999865469</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>70000</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>5.5172108999977354</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>70000</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>5.3989683999971021</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>70000</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>5.5347767999919597</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>70000</v>
       </c>
@@ -10377,7 +10377,7 @@
         <v>5.6479407000151696</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>70000</v>
       </c>
@@ -10412,7 +10412,7 @@
         <v>5.4130385000025854</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>70000</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>5.4161419000156457</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>70000</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>5.4464356000098633</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>70000</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>5.6166250000096616</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>70000</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>5.5304822000034619</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>70000</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>5.5718799000023864</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>70000</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>5.5633484999852953</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>70000</v>
       </c>
@@ -10657,7 +10657,7 @@
         <v>5.5850031000009039</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>70000</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>5.5347347000060836</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>70000</v>
       </c>
@@ -10727,7 +10727,7 @@
         <v>5.3718701000034343</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>70000</v>
       </c>
@@ -10762,7 +10762,7 @@
         <v>5.503811599992332</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>70000</v>
       </c>
@@ -10797,7 +10797,7 @@
         <v>5.4048397000005934</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>70000</v>
       </c>
@@ -10832,7 +10832,7 @@
         <v>5.3995544999925187</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>70000</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>5.5285912999970606</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>70000</v>
       </c>
@@ -10902,7 +10902,7 @@
         <v>5.4736036000103923</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>70000</v>
       </c>
@@ -10937,7 +10937,7 @@
         <v>5.5013610000023618</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>70000</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>5.4882464999973308</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>70000</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>5.5281380000087674</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>70000</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>5.4136193999875104</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>70000</v>
       </c>
@@ -11077,7 +11077,7 @@
         <v>5.617174500002875</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>70000</v>
       </c>
@@ -11112,7 +11112,7 @@
         <v>5.5348951000196394</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>70000</v>
       </c>
@@ -11147,7 +11147,7 @@
         <v>5.5336121999862371</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>70000</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>5.5184537000022829</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>70000</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>5.7365925000049174</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>70000</v>
       </c>
@@ -11252,7 +11252,7 @@
         <v>5.4973973999876762</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>70000</v>
       </c>
@@ -11287,7 +11287,7 @@
         <v>5.4988298999960534</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>70000</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>5.5905288999929326</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>70000</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>5.4938764999969862</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>70000</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>5.3953062999935364</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>70000</v>
       </c>
@@ -11427,7 +11427,7 @@
         <v>5.6602434999949756</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>70000</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>5.6454630000080206</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>70000</v>
       </c>
@@ -11497,7 +11497,7 @@
         <v>5.5846527999965474</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>70000</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>5.5755204999877606</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>70000</v>
       </c>
@@ -11567,7 +11567,7 @@
         <v>5.6009620999975596</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>70000</v>
       </c>
@@ -11602,7 +11602,7 @@
         <v>5.6116392999974778</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>70000</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>5.5959707000001799</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>70000</v>
       </c>
@@ -11672,7 +11672,7 @@
         <v>5.6165087999979733</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>70000</v>
       </c>
@@ -11707,7 +11707,7 @@
         <v>5.6554116999905091</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>70000</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>5.4286443000019062</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>70000</v>
       </c>
@@ -11777,7 +11777,7 @@
         <v>5.4205696999997599</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>70000</v>
       </c>
@@ -11812,7 +11812,7 @@
         <v>5.3985808999859728</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>70000</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>5.3885965999943437</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>70000</v>
       </c>
@@ -11882,7 +11882,7 @@
         <v>5.5135240000090562</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>70000</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>5.6957664000074146</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>70000</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>5.6080256000132067</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>70000</v>
       </c>
@@ -11987,7 +11987,7 @@
         <v>5.7904736999917077</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>70000</v>
       </c>
@@ -12022,7 +12022,7 @@
         <v>5.4898987999913524</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>70000</v>
       </c>
@@ -12057,7 +12057,7 @@
         <v>5.5945358000026317</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>70000</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>5.5469640000083018</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>70000</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>5.4908743999985754</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>70000</v>
       </c>
@@ -12162,7 +12162,7 @@
         <v>5.5923691999923903</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>70000</v>
       </c>
@@ -12197,7 +12197,7 @@
         <v>5.632353900000453</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>70000</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>5.3709352999867406</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>70000</v>
       </c>
@@ -12267,7 +12267,7 @@
         <v>5.6315172999893548</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>70000</v>
       </c>
@@ -12302,7 +12302,7 @@
         <v>5.5436397000012221</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>70000</v>
       </c>
@@ -12337,7 +12337,7 @@
         <v>5.6179967000061879</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>70000</v>
       </c>
@@ -12372,7 +12372,7 @@
         <v>5.5271779999893624</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>70000</v>
       </c>
@@ -12407,7 +12407,7 @@
         <v>5.4870652999961749</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>70000</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>5.6252593999961391</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>70000</v>
       </c>
@@ -12477,7 +12477,7 @@
         <v>5.609474400000181</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>70000</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>5.5344228999892948</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>70000</v>
       </c>
@@ -12547,7 +12547,7 @@
         <v>5.66388820001157</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>70000</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>5.6976474000111921</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>70000</v>
       </c>
@@ -12617,7 +12617,7 @@
         <v>5.483169099999941</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>70000</v>
       </c>
@@ -12652,7 +12652,7 @@
         <v>5.6228725999972076</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>70000</v>
       </c>
@@ -12687,7 +12687,7 @@
         <v>5.5762456999946153</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>70000</v>
       </c>
@@ -12722,7 +12722,7 @@
         <v>5.6415805999859003</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>70000</v>
       </c>
@@ -12757,7 +12757,7 @@
         <v>5.4804294000059599</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>70000</v>
       </c>
@@ -12792,7 +12792,7 @@
         <v>5.3574181000003591</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>70000</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>5.3712397999915993</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>70000</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>5.4004716000054032</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>70000</v>
       </c>
@@ -12897,7 +12897,7 @@
         <v>5.3194586999888998</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>70000</v>
       </c>
@@ -12932,7 +12932,7 @@
         <v>5.6496053999871947</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>70000</v>
       </c>
@@ -12967,7 +12967,7 @@
         <v>5.5344863999926019</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>70000</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>5.5536712000030093</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>70000</v>
       </c>
@@ -13037,7 +13037,7 @@
         <v>5.5071129000134533</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>70000</v>
       </c>
@@ -13072,7 +13072,7 @@
         <v>5.5292266000033123</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>70000</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>5.4909938999917358</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>70000</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>5.5465432000055443</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>70000</v>
       </c>
@@ -13177,7 +13177,7 @@
         <v>5.4590059999900404</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>70000</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>5.4736427000170806</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>70000</v>
       </c>
@@ -13247,7 +13247,7 @@
         <v>5.9256452000117861</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>70000</v>
       </c>
@@ -13282,7 +13282,7 @@
         <v>8.7022127999953227</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>70000</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>7.5487007000047024</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>70000</v>
       </c>
@@ -13352,7 +13352,7 @@
         <v>5.7690268000005744</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>70000</v>
       </c>
@@ -13387,7 +13387,7 @@
         <v>5.1563337999978103</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>70000</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>5.1824070000002393</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>70000</v>
       </c>
@@ -13457,7 +13457,7 @@
         <v>6.3845861000008881</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>70000</v>
       </c>
@@ -13492,7 +13492,7 @@
         <v>5.1972315000020899</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>70000</v>
       </c>
@@ -13527,7 +13527,7 @@
         <v>4.7006769999861717</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>70000</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>4.5645587999897543</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>70000</v>
       </c>
@@ -13597,7 +13597,7 @@
         <v>4.5141120000043884</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>70000</v>
       </c>
@@ -13632,7 +13632,7 @@
         <v>4.864603400012129</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>70000</v>
       </c>
@@ -13667,7 +13667,7 @@
         <v>4.4946021000068868</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>70000</v>
       </c>
@@ -13702,7 +13702,7 @@
         <v>4.5765301000210457</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>70000</v>
       </c>
@@ -13737,7 +13737,7 @@
         <v>4.6624580000061542</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>70000</v>
       </c>
@@ -13772,7 +13772,7 @@
         <v>4.5590339000045788</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>70000</v>
       </c>
@@ -13807,7 +13807,7 @@
         <v>5.2118497000046773</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>70000</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>4.8484873000124944</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>70000</v>
       </c>
@@ -13877,7 +13877,7 @@
         <v>4.5169654000201263</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>70000</v>
       </c>
@@ -13912,7 +13912,7 @@
         <v>4.6380415999883553</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>70000</v>
       </c>
@@ -13947,7 +13947,7 @@
         <v>4.6955578999913996</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>70000</v>
       </c>
@@ -13982,7 +13982,7 @@
         <v>4.5501588999904934</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>70000</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>4.5285080999892671</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>70000</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>4.5849701999977697</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>70000</v>
       </c>
@@ -14087,7 +14087,7 @@
         <v>4.7370612999948207</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>70000</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>4.6931349999940721</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>70000</v>
       </c>
@@ -14157,7 +14157,7 @@
         <v>4.5657396000169683</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>70000</v>
       </c>
@@ -14192,7 +14192,7 @@
         <v>4.6579338999872562</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>70000</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>4.8646519999892917</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>70000</v>
       </c>
@@ -14262,7 +14262,7 @@
         <v>5.261319099998218</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>70000</v>
       </c>
@@ -14297,7 +14297,7 @@
         <v>5.0402452999987872</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>70000</v>
       </c>
@@ -14332,7 +14332,7 @@
         <v>5.3113833999959752</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>70000</v>
       </c>
@@ -14367,7 +14367,7 @@
         <v>4.628458999999566</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>70000</v>
       </c>
@@ -14402,7 +14402,7 @@
         <v>4.6917124000028707</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>70000</v>
       </c>
@@ -14437,7 +14437,7 @@
         <v>4.6777011999947717</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>70000</v>
       </c>
@@ -14472,7 +14472,7 @@
         <v>4.6111103000148432</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>70000</v>
       </c>
@@ -14507,7 +14507,7 @@
         <v>4.7697809999954188</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>70000</v>
       </c>
@@ -14542,7 +14542,7 @@
         <v>4.8671342999878107</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>70000</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>5.1215529999899454</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>70000</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>4.5786801999929594</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>70000</v>
       </c>
@@ -14647,7 +14647,7 @@
         <v>4.4873394000169364</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>70000</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>4.3980791999929352</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>70000</v>
       </c>
@@ -14717,7 +14717,7 @@
         <v>4.4200246999971569</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>70000</v>
       </c>
@@ -14752,7 +14752,7 @@
         <v>4.4822079000005033</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>70000</v>
       </c>
@@ -14787,7 +14787,7 @@
         <v>4.4898767999984557</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>70000</v>
       </c>
@@ -14822,7 +14822,7 @@
         <v>4.4411232999991634</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>70000</v>
       </c>
@@ -14865,18 +14865,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -14899,7 +14899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>50</v>
       </c>
@@ -14922,7 +14922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>50</v>
       </c>
@@ -14945,7 +14945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>50</v>
       </c>
@@ -14968,7 +14968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>50</v>
       </c>
@@ -14991,7 +14991,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>50</v>
       </c>
@@ -15014,7 +15014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>50</v>
       </c>
@@ -15037,7 +15037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>80</v>
       </c>
@@ -15060,7 +15060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>80</v>
       </c>
@@ -15083,7 +15083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>80</v>
       </c>
@@ -15106,7 +15106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>80</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>80</v>
       </c>
@@ -15152,7 +15152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>80</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>100</v>
       </c>
@@ -15198,7 +15198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>100</v>
       </c>
@@ -15221,7 +15221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>100</v>
       </c>
@@ -15244,7 +15244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>100</v>
       </c>
@@ -15267,7 +15267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>100</v>
       </c>
@@ -15290,7 +15290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>100</v>
       </c>
@@ -15313,7 +15313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>120</v>
       </c>
@@ -15336,7 +15336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>120</v>
       </c>
@@ -15359,7 +15359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>120</v>
       </c>
@@ -15382,7 +15382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>120</v>
       </c>
@@ -15405,7 +15405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>120</v>
       </c>
@@ -15428,7 +15428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>120</v>
       </c>
@@ -15451,7 +15451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>150</v>
       </c>
@@ -15474,7 +15474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>150</v>
       </c>
@@ -15497,7 +15497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>150</v>
       </c>
@@ -15520,7 +15520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>150</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>150</v>
       </c>
@@ -15566,7 +15566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>150</v>
       </c>
@@ -15589,7 +15589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>200</v>
       </c>
@@ -15612,7 +15612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>200</v>
       </c>
@@ -15635,7 +15635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>200</v>
       </c>
@@ -15658,7 +15658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>200</v>
       </c>
@@ -15681,7 +15681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>200</v>
       </c>
@@ -15704,7 +15704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>200</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>500</v>
       </c>
@@ -15750,7 +15750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>500</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>500</v>
       </c>
@@ -15796,7 +15796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>500</v>
       </c>
@@ -15819,7 +15819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>500</v>
       </c>
@@ -15842,7 +15842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>500</v>
       </c>
@@ -15873,14 +15873,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E265F2D-4BDB-4332-91AD-88FABCDE77F4}">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>50</v>
       </c>
@@ -15936,7 +15936,7 @@
         <v>525.25370370370365</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>80</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>370.11018518518512</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>364.9175925925926</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>120</v>
       </c>
@@ -16035,7 +16035,7 @@
         <v>337.22222222222223</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>150</v>
       </c>
@@ -16068,7 +16068,7 @@
         <v>363.35092592592588</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>200</v>
       </c>
@@ -16101,7 +16101,7 @@
         <v>330.38425925925918</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>500</v>
       </c>
@@ -16134,7 +16134,7 @@
         <v>347.58518518518514</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10">
         <f>AVERAGE(B2:B8)</f>
         <v>388.05238095238076</v>
@@ -16169,9 +16169,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>50</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>361.72222222222217</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>80</v>
       </c>
@@ -16240,7 +16240,7 @@
         <v>340.91111111111121</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
@@ -16263,7 +16263,7 @@
         <v>313.8555555555555</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>120</v>
       </c>
@@ -16286,7 +16286,7 @@
         <v>305.91666666666669</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>150</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>353.51111111111112</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>200</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>350.01666666666671</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>500</v>
       </c>
@@ -16363,17 +16363,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD075B78-C560-45B4-82DD-6832EAF8A444}">
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -16405,7 +16405,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>50</v>
       </c>
@@ -16437,7 +16437,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>80</v>
       </c>
@@ -16475,7 +16475,7 @@
         <v>101.25638696181393</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>100</v>
       </c>
@@ -16513,7 +16513,7 @@
         <v>116.72029457180238</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>120</v>
       </c>
@@ -16550,7 +16550,7 @@
         <v>73.808441403547434</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>150</v>
       </c>
@@ -16587,7 +16587,7 @@
         <v>100.98374280994841</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>200</v>
       </c>
@@ -16624,7 +16624,7 @@
         <v>106.66357347130749</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>500</v>
       </c>
@@ -16661,7 +16661,7 @@
         <v>105.47308225273461</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>750</v>
       </c>
@@ -16674,11 +16674,11 @@
         <v>103.22199999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -16707,7 +16707,7 @@
         <v>361.97222222222229</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -16736,17 +16736,17 @@
         <v>128.07988345739059</v>
       </c>
     </row>
-    <row r="19" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N19" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N34" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N50" s="7" t="s">
         <v>31</v>
       </c>
